--- a/unified_plan_metrics_template.xlsx
+++ b/unified_plan_metrics_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chaffeyccd-my.sharepoint.com/personal/joseph_cascio_chaffey_edu/Documents/Research Analyst/Surveys and Reports/Combining Initiative Reports/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="154" documentId="8_{0966D836-5100-49BC-8A45-6686B0C0AF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4FBAEE48-8FD3-4E5A-83FF-FFE458D67209}"/>
+  <xr:revisionPtr revIDLastSave="176" documentId="8_{0966D836-5100-49BC-8A45-6686B0C0AF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CDC2DFC0-D2B0-4793-9F57-83234661FF44}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BFF79AE2-E76B-441F-B8D7-30B63CE1804C}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BFF79AE2-E76B-441F-B8D7-30B63CE1804C}"/>
   </bookViews>
   <sheets>
     <sheet name="master" sheetId="1" r:id="rId1"/>
@@ -428,9 +428,6 @@
     <t>Course Success Rate</t>
   </si>
   <si>
-    <t>1: Success</t>
-  </si>
-  <si>
     <t>1.3 Improve course success rates</t>
   </si>
   <si>
@@ -731,9 +728,6 @@
     <t>Transfers to 4-Year Institutions</t>
   </si>
   <si>
-    <t>1: Success; 3: Career</t>
-  </si>
-  <si>
     <t>1.4 Increase transfer rates to four-year institutions; 3.2 Strengthen career pathways</t>
   </si>
   <si>
@@ -749,9 +743,6 @@
     <t>Career Education (CTE) Momentum</t>
   </si>
   <si>
-    <t>3: Career</t>
-  </si>
-  <si>
     <t>3.1 Align programs with regional workforce needs</t>
   </si>
   <si>
@@ -800,9 +791,6 @@
     <t>All Employees</t>
   </si>
   <si>
-    <t>2: Learning</t>
-  </si>
-  <si>
     <t>2.1 Expand professional learning opportunities</t>
   </si>
   <si>
@@ -890,9 +878,6 @@
     <t>Campus Climate &amp; Equity</t>
   </si>
   <si>
-    <t>4: Equity</t>
-  </si>
-  <si>
     <t>M-043</t>
   </si>
   <si>
@@ -1878,6 +1863,21 @@
   </si>
   <si>
     <t>Metric Trait(s) / Initiative Alignment (Values separated with ";")</t>
+  </si>
+  <si>
+    <t>Goal 1: Success</t>
+  </si>
+  <si>
+    <t>Goal 1: Success; Goal 3: Career</t>
+  </si>
+  <si>
+    <t>Goal 2: Learning</t>
+  </si>
+  <si>
+    <t>Goal 3: Career</t>
+  </si>
+  <si>
+    <t>Goal 4: Equity</t>
   </si>
 </sst>
 </file>
@@ -2505,7 +2505,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2616,32 +2616,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -2652,19 +2631,10 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="10" xfId="43" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2733,86 +2703,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="4" formatCode="#,##0.00"/>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -3060,6 +2950,86 @@
       </border>
     </dxf>
     <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="4" formatCode="#,##0.00"/>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
@@ -3352,24 +3322,24 @@
     <tableColumn id="7" xr3:uid="{7100813D-8C65-4EBF-9DDD-C8CA3A40B451}" name="2023-2024" dataDxfId="21"/>
     <tableColumn id="8" xr3:uid="{DB509304-3EB1-4D4D-B714-6AF965CB0BA7}" name="2024-2025" dataDxfId="20"/>
     <tableColumn id="9" xr3:uid="{F5EAFEFD-FC0A-487F-8525-1C93255BD17F}" name="2025-2026" dataDxfId="19"/>
-    <tableColumn id="22" xr3:uid="{19854763-5938-48CE-8523-23258BFF1C3E}" name="EMP Baseline (2025-2026 Yr 0)" dataDxfId="4"/>
-    <tableColumn id="23" xr3:uid="{14F0D8E9-D836-4B80-94D3-7B8418392D1A}" name="EMP Target Goal" dataDxfId="3"/>
-    <tableColumn id="24" xr3:uid="{FA021FCD-2B93-4B93-B866-74FFE5B66D07}" name="Strategic Plan Baseline (2024-2025 Yr 0)" dataDxfId="2"/>
-    <tableColumn id="25" xr3:uid="{D5AB3269-32D4-42B9-BB3A-AA4B7E4FFDFF}" name="Strategic Plan Target Goal (2026-2030)" dataDxfId="1"/>
-    <tableColumn id="10" xr3:uid="{75661E75-33EF-41F7-82E4-B6310A3593CE}" name="Metric Category(s) (Values separated with &quot;;&quot;)" dataDxfId="18"/>
-    <tableColumn id="11" xr3:uid="{DA1B6D5A-215E-41EA-9F08-24EF4EC80064}" name="Parent Metric / Group(s) (Values separated with &quot;;&quot;)" dataDxfId="17"/>
-    <tableColumn id="12" xr3:uid="{820F094D-7B9E-47B0-8C6E-0D83F1170158}" name="Disaggregation / Sub-Group" dataDxfId="16"/>
-    <tableColumn id="13" xr3:uid="{69499416-0BBF-4736-A627-F5FF57D01BD6}" name="Data Source(s) (Values separated with &quot;;&quot;)" dataDxfId="15"/>
-    <tableColumn id="14" xr3:uid="{380BCA21-1816-46A2-8F4A-8733D846638C}" name="Metric Trait(s) / Initiative Alignment (Values separated with &quot;;&quot;)" dataDxfId="14"/>
-    <tableColumn id="15" xr3:uid="{720F9919-B516-4F6D-A4E9-AFAC3AAE8FE8}" name="Metric Unit / Format" dataDxfId="13"/>
-    <tableColumn id="16" xr3:uid="{B95953D7-6301-4CC6-AAAA-00EC45DC8696}" name="Metric Definition" dataDxfId="12"/>
-    <tableColumn id="17" xr3:uid="{16703B11-181A-4C28-89FA-B74B6009D141}" name="EMP Plan Area(s) (Values separated with &quot;;&quot;)" dataDxfId="11"/>
-    <tableColumn id="18" xr3:uid="{A85AE38E-DD71-47D8-9B3F-93F3665251C9}" name="EMP Goal" dataDxfId="10"/>
-    <tableColumn id="19" xr3:uid="{B5229022-4623-4A51-8A04-59F34185791D}" name="Strategic Plan Goal" dataDxfId="9"/>
-    <tableColumn id="20" xr3:uid="{68B3561C-0B72-42FA-B91B-F32D508D228A}" name="Strategic Plan Objective" dataDxfId="8"/>
-    <tableColumn id="21" xr3:uid="{E6E125FC-4BE6-440C-9CF6-403D81BF954C}" name="Guided Pathways Alignment" dataDxfId="7"/>
-    <tableColumn id="26" xr3:uid="{CBEEC815-9C36-494D-846B-F0E62B179CB5}" name="Responsible Party(s) (Values separated with &quot;;&quot;)" dataDxfId="6"/>
-    <tableColumn id="27" xr3:uid="{FD86AE70-9F9B-455E-A273-BF718DEAEFCA}" name="Notes &amp; Methodology Nuances" dataDxfId="5"/>
+    <tableColumn id="22" xr3:uid="{19854763-5938-48CE-8523-23258BFF1C3E}" name="EMP Baseline (2025-2026 Yr 0)" dataDxfId="18"/>
+    <tableColumn id="23" xr3:uid="{14F0D8E9-D836-4B80-94D3-7B8418392D1A}" name="EMP Target Goal" dataDxfId="17"/>
+    <tableColumn id="24" xr3:uid="{FA021FCD-2B93-4B93-B866-74FFE5B66D07}" name="Strategic Plan Baseline (2024-2025 Yr 0)" dataDxfId="16"/>
+    <tableColumn id="25" xr3:uid="{D5AB3269-32D4-42B9-BB3A-AA4B7E4FFDFF}" name="Strategic Plan Target Goal (2026-2030)" dataDxfId="15"/>
+    <tableColumn id="10" xr3:uid="{75661E75-33EF-41F7-82E4-B6310A3593CE}" name="Metric Category(s) (Values separated with &quot;;&quot;)" dataDxfId="14"/>
+    <tableColumn id="11" xr3:uid="{DA1B6D5A-215E-41EA-9F08-24EF4EC80064}" name="Parent Metric / Group(s) (Values separated with &quot;;&quot;)" dataDxfId="13"/>
+    <tableColumn id="12" xr3:uid="{820F094D-7B9E-47B0-8C6E-0D83F1170158}" name="Disaggregation / Sub-Group" dataDxfId="12"/>
+    <tableColumn id="13" xr3:uid="{69499416-0BBF-4736-A627-F5FF57D01BD6}" name="Data Source(s) (Values separated with &quot;;&quot;)" dataDxfId="11"/>
+    <tableColumn id="14" xr3:uid="{380BCA21-1816-46A2-8F4A-8733D846638C}" name="Metric Trait(s) / Initiative Alignment (Values separated with &quot;;&quot;)" dataDxfId="10"/>
+    <tableColumn id="15" xr3:uid="{720F9919-B516-4F6D-A4E9-AFAC3AAE8FE8}" name="Metric Unit / Format" dataDxfId="9"/>
+    <tableColumn id="16" xr3:uid="{B95953D7-6301-4CC6-AAAA-00EC45DC8696}" name="Metric Definition" dataDxfId="8"/>
+    <tableColumn id="17" xr3:uid="{16703B11-181A-4C28-89FA-B74B6009D141}" name="EMP Plan Area(s) (Values separated with &quot;;&quot;)" dataDxfId="7"/>
+    <tableColumn id="18" xr3:uid="{A85AE38E-DD71-47D8-9B3F-93F3665251C9}" name="EMP Goal" dataDxfId="6"/>
+    <tableColumn id="19" xr3:uid="{B5229022-4623-4A51-8A04-59F34185791D}" name="Strategic Plan Goal" dataDxfId="5"/>
+    <tableColumn id="20" xr3:uid="{68B3561C-0B72-42FA-B91B-F32D508D228A}" name="Strategic Plan Objective" dataDxfId="4"/>
+    <tableColumn id="21" xr3:uid="{E6E125FC-4BE6-440C-9CF6-403D81BF954C}" name="Guided Pathways Alignment" dataDxfId="3"/>
+    <tableColumn id="26" xr3:uid="{CBEEC815-9C36-494D-846B-F0E62B179CB5}" name="Responsible Party(s) (Values separated with &quot;;&quot;)" dataDxfId="2"/>
+    <tableColumn id="27" xr3:uid="{FD86AE70-9F9B-455E-A273-BF718DEAEFCA}" name="Notes &amp; Methodology Nuances" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3724,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="C1" s="22" t="s">
         <v>1</v>
@@ -3760,19 +3730,19 @@
         <v>18</v>
       </c>
       <c r="N1" s="24" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="O1" s="24" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="P1" s="24" t="s">
         <v>2</v>
       </c>
       <c r="Q1" s="24" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="R1" s="24" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="S1" s="24" t="s">
         <v>6</v>
@@ -3781,7 +3751,7 @@
         <v>7</v>
       </c>
       <c r="U1" s="24" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="V1" s="24" t="s">
         <v>3</v>
@@ -3796,80 +3766,80 @@
         <v>8</v>
       </c>
       <c r="Z1" s="24" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="AA1" s="25" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="30" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="B2" s="41" t="s">
-        <v>532</v>
-      </c>
-      <c r="C2" s="41" t="s">
+      <c r="B2" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D2" s="48">
+      <c r="D2" s="32">
         <v>28796</v>
       </c>
-      <c r="E2" s="48">
+      <c r="E2" s="32">
         <v>28316</v>
       </c>
-      <c r="F2" s="48">
+      <c r="F2" s="32">
         <v>30505</v>
       </c>
-      <c r="G2" s="48">
+      <c r="G2" s="32">
         <v>33531</v>
       </c>
-      <c r="H2" s="48">
+      <c r="H2" s="32">
         <v>36077</v>
       </c>
-      <c r="I2" s="48">
+      <c r="I2" s="32">
         <v>36592</v>
       </c>
-      <c r="J2" s="53">
+      <c r="J2" s="45">
         <v>36592</v>
       </c>
-      <c r="K2" s="43"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="46" t="s">
+      <c r="K2" s="36"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="O2" s="46" t="s">
+      <c r="O2" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="P2" s="46" t="s">
+      <c r="P2" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Q2" s="46" t="s">
+      <c r="Q2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="R2" s="46"/>
-      <c r="S2" s="46" t="s">
+      <c r="R2" s="4"/>
+      <c r="S2" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="T2" s="46" t="s">
+      <c r="T2" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="U2" s="46" t="s">
+      <c r="U2" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="V2" s="46" t="s">
+      <c r="V2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="W2" s="46"/>
-      <c r="X2" s="46"/>
-      <c r="Y2" s="46" t="s">
+      <c r="W2" s="4"/>
+      <c r="X2" s="4"/>
+      <c r="Y2" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="Z2" s="46" t="s">
+      <c r="Z2" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AA2" s="47" t="s">
+      <c r="AA2" s="20" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3881,7 +3851,7 @@
         <v>34</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="D3" s="15">
         <v>122183</v>
@@ -3938,13 +3908,13 @@
     </row>
     <row r="4" spans="1:27" ht="45" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>593</v>
+        <v>588</v>
       </c>
       <c r="D4" s="16">
         <v>14513.1</v>
@@ -3977,7 +3947,7 @@
         <v>38</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="Q4" s="4" t="s">
         <v>41</v>
@@ -4006,18 +3976,18 @@
         <v>28</v>
       </c>
       <c r="AA4" s="20" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>595</v>
+        <v>590</v>
       </c>
       <c r="D5" s="16"/>
       <c r="E5" s="16"/>
@@ -4042,10 +4012,10 @@
         <v>38</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="R5" s="4" t="s">
         <v>42</v>
@@ -4071,1023 +4041,1023 @@
         <v>28</v>
       </c>
       <c r="AA5" s="20" t="s">
-        <v>596</v>
+        <v>591</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="40" t="s">
+      <c r="A6" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="B6" s="41" t="s">
+      <c r="B6" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15">
+        <v>1683.81</v>
+      </c>
+      <c r="G6" s="15">
+        <v>1279.95</v>
+      </c>
+      <c r="H6" s="15">
+        <v>1233.7</v>
+      </c>
+      <c r="I6" s="15">
+        <v>1367.6</v>
+      </c>
+      <c r="J6" s="36">
+        <v>1367.6</v>
+      </c>
+      <c r="K6" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="L6" s="4"/>
+      <c r="M6" s="4"/>
+      <c r="N6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="S6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="T6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="V6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="W6" s="4"/>
+      <c r="X6" s="4"/>
+      <c r="Y6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z6" s="4"/>
+      <c r="AA6" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+      <c r="F7" s="15">
+        <v>1453.6</v>
+      </c>
+      <c r="G7" s="15">
+        <v>1110.97</v>
+      </c>
+      <c r="H7" s="15">
+        <v>1147.79</v>
+      </c>
+      <c r="I7" s="15">
+        <v>1348.16</v>
+      </c>
+      <c r="J7" s="36">
+        <v>1348.16</v>
+      </c>
+      <c r="K7" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="L7" s="4"/>
+      <c r="M7" s="4"/>
+      <c r="N7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q7" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="S7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="T7" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="V7" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="W7" s="4"/>
+      <c r="X7" s="4"/>
+      <c r="Y7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z7" s="4"/>
+      <c r="AA7" s="20" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="15">
+        <v>1199.52</v>
+      </c>
+      <c r="G8" s="15">
+        <v>1482.93</v>
+      </c>
+      <c r="H8" s="15">
+        <v>1220.21</v>
+      </c>
+      <c r="I8" s="15">
+        <v>1802.11</v>
+      </c>
+      <c r="J8" s="36">
+        <v>1802.11</v>
+      </c>
+      <c r="K8" s="36"/>
+      <c r="L8" s="4"/>
+      <c r="M8" s="4"/>
+      <c r="N8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="R8" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="C6" s="41" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="54"/>
-      <c r="E6" s="54"/>
-      <c r="F6" s="54">
-        <v>1683.81</v>
-      </c>
-      <c r="G6" s="54">
-        <v>1279.95</v>
-      </c>
-      <c r="H6" s="54">
-        <v>1233.7</v>
-      </c>
-      <c r="I6" s="54">
-        <v>1367.6</v>
-      </c>
-      <c r="J6" s="43">
-        <v>1367.6</v>
-      </c>
-      <c r="K6" s="43" t="s">
-        <v>48</v>
-      </c>
-      <c r="L6" s="46"/>
-      <c r="M6" s="46"/>
-      <c r="N6" s="46" t="s">
+      <c r="S8" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="T8" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="U8" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="V8" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W8" s="4"/>
+      <c r="X8" s="4"/>
+      <c r="Y8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z8" s="4"/>
+      <c r="AA8" s="20" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A9" s="18" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+      <c r="F9" s="15">
+        <v>56.76</v>
+      </c>
+      <c r="G9" s="15">
+        <v>104.07</v>
+      </c>
+      <c r="H9" s="15">
+        <v>106.81</v>
+      </c>
+      <c r="I9" s="15">
+        <v>149.16999999999999</v>
+      </c>
+      <c r="J9" s="36">
+        <v>149.16999999999999</v>
+      </c>
+      <c r="K9" s="36"/>
+      <c r="L9" s="4"/>
+      <c r="M9" s="4"/>
+      <c r="N9" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="O6" s="46" t="s">
+      <c r="O9" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="P6" s="46" t="s">
-        <v>45</v>
-      </c>
-      <c r="Q6" s="46" t="s">
+      <c r="P9" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q9" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="R6" s="46" t="s">
+      <c r="R9" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="S9" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="T9" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="U9" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="V9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W9" s="4"/>
+      <c r="X9" s="4"/>
+      <c r="Y9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z9" s="4"/>
+      <c r="AA9" s="20" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A10" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15"/>
+      <c r="F10" s="15">
+        <v>218.36</v>
+      </c>
+      <c r="G10" s="15">
+        <v>106.6</v>
+      </c>
+      <c r="H10" s="15">
+        <v>155.51</v>
+      </c>
+      <c r="I10" s="15"/>
+      <c r="J10" s="36"/>
+      <c r="K10" s="36"/>
+      <c r="L10" s="4"/>
+      <c r="M10" s="4"/>
+      <c r="N10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="O10" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="P10" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q10" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="R10" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="S6" s="46" t="s">
+      <c r="S10" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="T6" s="46" t="s">
-        <v>46</v>
-      </c>
-      <c r="U6" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="V6" s="46" t="s">
-        <v>25</v>
-      </c>
-      <c r="W6" s="46"/>
-      <c r="X6" s="46"/>
-      <c r="Y6" s="46" t="s">
+      <c r="T10" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="U10" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="V10" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W10" s="4"/>
+      <c r="X10" s="4"/>
+      <c r="Y10" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="Z6" s="46"/>
-      <c r="AA6" s="47" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="40" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="41" t="s">
+      <c r="Z10" s="4"/>
+      <c r="AA10" s="20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D11" s="32">
+        <v>7515</v>
+      </c>
+      <c r="E11" s="32">
+        <v>6853</v>
+      </c>
+      <c r="F11" s="32">
+        <v>7190</v>
+      </c>
+      <c r="G11" s="32">
+        <v>7853</v>
+      </c>
+      <c r="H11" s="32">
+        <v>9301</v>
+      </c>
+      <c r="I11" s="32"/>
+      <c r="J11" s="36"/>
+      <c r="K11" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="L11" s="4"/>
+      <c r="M11" s="4"/>
+      <c r="N11" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="O11" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="P11" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q11" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="R11" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="C7" s="41" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" s="54"/>
-      <c r="E7" s="54"/>
-      <c r="F7" s="54">
-        <v>1453.6</v>
-      </c>
-      <c r="G7" s="54">
-        <v>1110.97</v>
-      </c>
-      <c r="H7" s="54">
-        <v>1147.79</v>
-      </c>
-      <c r="I7" s="54">
-        <v>1348.16</v>
-      </c>
-      <c r="J7" s="43">
-        <v>1348.16</v>
-      </c>
-      <c r="K7" s="43" t="s">
-        <v>48</v>
-      </c>
-      <c r="L7" s="46"/>
-      <c r="M7" s="46"/>
-      <c r="N7" s="46" t="s">
+      <c r="S11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="T11" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="U11" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="V11" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W11" s="4"/>
+      <c r="X11" s="4"/>
+      <c r="Y11" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z11" s="4"/>
+      <c r="AA11" s="20" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D12" s="32">
+        <v>15458</v>
+      </c>
+      <c r="E12" s="32">
+        <v>13884</v>
+      </c>
+      <c r="F12" s="32">
+        <v>14134</v>
+      </c>
+      <c r="G12" s="32">
+        <v>16152</v>
+      </c>
+      <c r="H12" s="32">
+        <v>17089</v>
+      </c>
+      <c r="I12" s="32"/>
+      <c r="J12" s="36"/>
+      <c r="K12" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="L12" s="4"/>
+      <c r="M12" s="4"/>
+      <c r="N12" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="O7" s="46" t="s">
-        <v>38</v>
-      </c>
-      <c r="P7" s="46" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q7" s="46" t="s">
-        <v>47</v>
-      </c>
-      <c r="R7" s="46" t="s">
+      <c r="O12" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="P12" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q12" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="R12" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="S12" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="T12" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="U12" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="V12" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W12" s="4"/>
+      <c r="X12" s="4"/>
+      <c r="Y12" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="Z12" s="4"/>
+      <c r="AA12" s="20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D13" s="32">
+        <v>1619</v>
+      </c>
+      <c r="E13" s="32">
+        <v>1243</v>
+      </c>
+      <c r="F13" s="32">
+        <v>566</v>
+      </c>
+      <c r="G13" s="32">
+        <v>588</v>
+      </c>
+      <c r="H13" s="32">
+        <v>625</v>
+      </c>
+      <c r="I13" s="32"/>
+      <c r="J13" s="37"/>
+      <c r="K13" s="37"/>
+      <c r="L13" s="4"/>
+      <c r="M13" s="4"/>
+      <c r="N13" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="O13" s="4" t="s">
+        <v>542</v>
+      </c>
+      <c r="P13" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q13" s="4" t="s">
+        <v>526</v>
+      </c>
+      <c r="R13" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="S7" s="46" t="s">
-        <v>39</v>
-      </c>
-      <c r="T7" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="U7" s="46" t="s">
-        <v>24</v>
-      </c>
-      <c r="V7" s="46" t="s">
-        <v>25</v>
-      </c>
-      <c r="W7" s="46"/>
-      <c r="X7" s="46"/>
-      <c r="Y7" s="46" t="s">
+      <c r="S13" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="T13" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="U13" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="V13" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W13" s="4"/>
+      <c r="X13" s="4"/>
+      <c r="Y13" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="Z7" s="46"/>
-      <c r="AA7" s="47" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" s="41" t="s">
-        <v>530</v>
-      </c>
-      <c r="C8" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="54"/>
-      <c r="E8" s="54"/>
-      <c r="F8" s="54">
-        <v>1199.52</v>
-      </c>
-      <c r="G8" s="54">
-        <v>1482.93</v>
-      </c>
-      <c r="H8" s="54">
-        <v>1220.21</v>
-      </c>
-      <c r="I8" s="54">
-        <v>1802.11</v>
-      </c>
-      <c r="J8" s="43">
-        <v>1802.11</v>
-      </c>
-      <c r="K8" s="43"/>
-      <c r="L8" s="46"/>
-      <c r="M8" s="46"/>
-      <c r="N8" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="O8" s="46" t="s">
-        <v>38</v>
-      </c>
-      <c r="P8" s="46" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q8" s="46" t="s">
-        <v>47</v>
-      </c>
-      <c r="R8" s="46" t="s">
-        <v>535</v>
-      </c>
-      <c r="S8" s="46" t="s">
-        <v>39</v>
-      </c>
-      <c r="T8" s="46" t="s">
-        <v>60</v>
-      </c>
-      <c r="U8" s="46" t="s">
-        <v>58</v>
-      </c>
-      <c r="V8" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="W8" s="46"/>
-      <c r="X8" s="46"/>
-      <c r="Y8" s="46" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z8" s="46"/>
-      <c r="AA8" s="47" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A9" s="40" t="s">
-        <v>62</v>
-      </c>
-      <c r="B9" s="41" t="s">
-        <v>530</v>
-      </c>
-      <c r="C9" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54">
-        <v>56.76</v>
-      </c>
-      <c r="G9" s="54">
-        <v>104.07</v>
-      </c>
-      <c r="H9" s="54">
-        <v>106.81</v>
-      </c>
-      <c r="I9" s="54">
-        <v>149.16999999999999</v>
-      </c>
-      <c r="J9" s="43">
-        <v>149.16999999999999</v>
-      </c>
-      <c r="K9" s="43"/>
-      <c r="L9" s="46"/>
-      <c r="M9" s="46"/>
-      <c r="N9" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="O9" s="46" t="s">
-        <v>38</v>
-      </c>
-      <c r="P9" s="46" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q9" s="46" t="s">
-        <v>47</v>
-      </c>
-      <c r="R9" s="46" t="s">
-        <v>535</v>
-      </c>
-      <c r="S9" s="46" t="s">
-        <v>39</v>
-      </c>
-      <c r="T9" s="46" t="s">
-        <v>65</v>
-      </c>
-      <c r="U9" s="46" t="s">
-        <v>58</v>
-      </c>
-      <c r="V9" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="W9" s="46"/>
-      <c r="X9" s="46"/>
-      <c r="Y9" s="46" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z9" s="46"/>
-      <c r="AA9" s="47" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A10" s="40" t="s">
-        <v>67</v>
-      </c>
-      <c r="B10" s="41" t="s">
-        <v>530</v>
-      </c>
-      <c r="C10" s="41" t="s">
-        <v>68</v>
-      </c>
-      <c r="D10" s="54"/>
-      <c r="E10" s="54"/>
-      <c r="F10" s="54">
-        <v>218.36</v>
-      </c>
-      <c r="G10" s="54">
-        <v>106.6</v>
-      </c>
-      <c r="H10" s="54">
-        <v>155.51</v>
-      </c>
-      <c r="I10" s="54"/>
-      <c r="J10" s="43"/>
-      <c r="K10" s="43"/>
-      <c r="L10" s="46"/>
-      <c r="M10" s="46"/>
-      <c r="N10" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="O10" s="46" t="s">
-        <v>38</v>
-      </c>
-      <c r="P10" s="46" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q10" s="46" t="s">
-        <v>47</v>
-      </c>
-      <c r="R10" s="46" t="s">
-        <v>42</v>
-      </c>
-      <c r="S10" s="46" t="s">
-        <v>39</v>
-      </c>
-      <c r="T10" s="46" t="s">
-        <v>71</v>
-      </c>
-      <c r="U10" s="46" t="s">
-        <v>70</v>
-      </c>
-      <c r="V10" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="W10" s="46"/>
-      <c r="X10" s="46"/>
-      <c r="Y10" s="46" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z10" s="46"/>
-      <c r="AA10" s="47" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="40" t="s">
-        <v>73</v>
-      </c>
-      <c r="B11" s="41" t="s">
-        <v>532</v>
-      </c>
-      <c r="C11" s="41" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11" s="48">
-        <v>7515</v>
-      </c>
-      <c r="E11" s="48">
-        <v>6853</v>
-      </c>
-      <c r="F11" s="48">
-        <v>7190</v>
-      </c>
-      <c r="G11" s="48">
-        <v>7853</v>
-      </c>
-      <c r="H11" s="48">
-        <v>9301</v>
-      </c>
-      <c r="I11" s="48"/>
-      <c r="J11" s="43"/>
-      <c r="K11" s="43" t="s">
-        <v>78</v>
-      </c>
-      <c r="L11" s="46"/>
-      <c r="M11" s="46"/>
-      <c r="N11" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="O11" s="46" t="s">
-        <v>547</v>
-      </c>
-      <c r="P11" s="46" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q11" s="46" t="s">
-        <v>531</v>
-      </c>
-      <c r="R11" s="46" t="s">
-        <v>535</v>
-      </c>
-      <c r="S11" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="T11" s="46" t="s">
-        <v>76</v>
-      </c>
-      <c r="U11" s="46" t="s">
-        <v>58</v>
-      </c>
-      <c r="V11" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="W11" s="46"/>
-      <c r="X11" s="46"/>
-      <c r="Y11" s="46" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z11" s="46"/>
-      <c r="AA11" s="47" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="40" t="s">
-        <v>80</v>
-      </c>
-      <c r="B12" s="41" t="s">
-        <v>532</v>
-      </c>
-      <c r="C12" s="41" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" s="48">
-        <v>15458</v>
-      </c>
-      <c r="E12" s="48">
-        <v>13884</v>
-      </c>
-      <c r="F12" s="48">
-        <v>14134</v>
-      </c>
-      <c r="G12" s="48">
-        <v>16152</v>
-      </c>
-      <c r="H12" s="48">
-        <v>17089</v>
-      </c>
-      <c r="I12" s="48"/>
-      <c r="J12" s="43"/>
-      <c r="K12" s="43" t="s">
-        <v>78</v>
-      </c>
-      <c r="L12" s="46"/>
-      <c r="M12" s="46"/>
-      <c r="N12" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="O12" s="46" t="s">
-        <v>547</v>
-      </c>
-      <c r="P12" s="46" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q12" s="46" t="s">
-        <v>531</v>
-      </c>
-      <c r="R12" s="46" t="s">
-        <v>535</v>
-      </c>
-      <c r="S12" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="T12" s="46" t="s">
-        <v>83</v>
-      </c>
-      <c r="U12" s="46" t="s">
-        <v>58</v>
-      </c>
-      <c r="V12" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="W12" s="46"/>
-      <c r="X12" s="46"/>
-      <c r="Y12" s="46" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z12" s="46"/>
-      <c r="AA12" s="47" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="B13" s="41" t="s">
-        <v>532</v>
-      </c>
-      <c r="C13" s="41" t="s">
-        <v>553</v>
-      </c>
-      <c r="D13" s="48">
-        <v>1619</v>
-      </c>
-      <c r="E13" s="48">
-        <v>1243</v>
-      </c>
-      <c r="F13" s="48">
-        <v>566</v>
-      </c>
-      <c r="G13" s="48">
-        <v>588</v>
-      </c>
-      <c r="H13" s="48">
-        <v>625</v>
-      </c>
-      <c r="I13" s="48"/>
-      <c r="J13" s="55"/>
-      <c r="K13" s="55"/>
-      <c r="L13" s="46"/>
-      <c r="M13" s="46"/>
-      <c r="N13" s="46" t="s">
-        <v>21</v>
-      </c>
-      <c r="O13" s="46" t="s">
-        <v>547</v>
-      </c>
-      <c r="P13" s="46" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q13" s="46" t="s">
-        <v>531</v>
-      </c>
-      <c r="R13" s="46" t="s">
-        <v>42</v>
-      </c>
-      <c r="S13" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="T13" s="46" t="s">
-        <v>87</v>
-      </c>
-      <c r="U13" s="46" t="s">
-        <v>70</v>
-      </c>
-      <c r="V13" s="46" t="s">
-        <v>59</v>
-      </c>
-      <c r="W13" s="46"/>
-      <c r="X13" s="46"/>
-      <c r="Y13" s="46" t="s">
-        <v>30</v>
-      </c>
-      <c r="Z13" s="46"/>
-      <c r="AA13" s="47" t="s">
+      <c r="Z13" s="4"/>
+      <c r="AA13" s="20" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="40" t="s">
+      <c r="A14" s="18" t="s">
         <v>89</v>
       </c>
-      <c r="B14" s="41" t="s">
-        <v>530</v>
-      </c>
-      <c r="C14" s="41" t="s">
+      <c r="B14" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D14" s="56"/>
-      <c r="E14" s="56"/>
-      <c r="F14" s="56">
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46">
         <v>0.78200000000000003</v>
       </c>
-      <c r="G14" s="56">
+      <c r="G14" s="46">
         <v>0.81299999999999994</v>
       </c>
-      <c r="H14" s="56">
+      <c r="H14" s="46">
         <v>0.82</v>
       </c>
-      <c r="I14" s="56">
+      <c r="I14" s="46">
         <v>0.88200000000000001</v>
       </c>
-      <c r="J14" s="55">
+      <c r="J14" s="37">
         <v>0.88200000000000001</v>
       </c>
-      <c r="K14" s="55">
+      <c r="K14" s="37">
         <v>0.9</v>
       </c>
-      <c r="L14" s="46"/>
-      <c r="M14" s="46"/>
-      <c r="N14" s="46" t="s">
+      <c r="L14" s="4"/>
+      <c r="M14" s="4"/>
+      <c r="N14" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="O14" s="46" t="s">
+      <c r="O14" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="P14" s="46" t="s">
+      <c r="P14" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Q14" s="46" t="s">
+      <c r="Q14" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="R14" s="46"/>
-      <c r="S14" s="46" t="s">
+      <c r="R14" s="4"/>
+      <c r="S14" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="T14" s="46" t="s">
+      <c r="T14" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="U14" s="46" t="s">
+      <c r="U14" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="V14" s="46" t="s">
+      <c r="V14" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="W14" s="46"/>
-      <c r="X14" s="46"/>
-      <c r="Y14" s="46" t="s">
+      <c r="W14" s="4"/>
+      <c r="X14" s="4"/>
+      <c r="Y14" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="Z14" s="46"/>
-      <c r="AA14" s="47" t="s">
+      <c r="Z14" s="4"/>
+      <c r="AA14" s="20" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="40" t="s">
+      <c r="A15" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="B15" s="41" t="s">
-        <v>530</v>
-      </c>
-      <c r="C15" s="41" t="s">
+      <c r="B15" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54">
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15">
         <v>12.53</v>
       </c>
-      <c r="G15" s="54">
+      <c r="G15" s="15">
         <v>13.14</v>
       </c>
-      <c r="H15" s="54">
+      <c r="H15" s="15">
         <v>13.16</v>
       </c>
-      <c r="I15" s="54">
+      <c r="I15" s="15">
         <v>14.09</v>
       </c>
-      <c r="J15" s="43">
+      <c r="J15" s="36">
         <v>14.09</v>
       </c>
-      <c r="K15" s="43">
+      <c r="K15" s="36">
         <v>15</v>
       </c>
-      <c r="L15" s="46"/>
-      <c r="M15" s="46"/>
-      <c r="N15" s="46" t="s">
+      <c r="L15" s="4"/>
+      <c r="M15" s="4"/>
+      <c r="N15" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="O15" s="46" t="s">
+      <c r="O15" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="P15" s="46" t="s">
+      <c r="P15" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Q15" s="46" t="s">
+      <c r="Q15" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="R15" s="46"/>
-      <c r="S15" s="46" t="s">
+      <c r="R15" s="4"/>
+      <c r="S15" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="T15" s="46" t="s">
+      <c r="T15" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="U15" s="46" t="s">
+      <c r="U15" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="V15" s="46" t="s">
+      <c r="V15" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="W15" s="46"/>
-      <c r="X15" s="46"/>
-      <c r="Y15" s="46" t="s">
+      <c r="W15" s="4"/>
+      <c r="X15" s="4"/>
+      <c r="Y15" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="Z15" s="46"/>
-      <c r="AA15" s="47" t="s">
+      <c r="Z15" s="4"/>
+      <c r="AA15" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A16" s="40" t="s">
+      <c r="A16" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="B16" s="41" t="s">
-        <v>530</v>
-      </c>
-      <c r="C16" s="41" t="s">
+      <c r="B16" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D16" s="57"/>
-      <c r="E16" s="57"/>
-      <c r="F16" s="57">
+      <c r="D16" s="47"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="47">
         <v>0.76</v>
       </c>
-      <c r="G16" s="57">
+      <c r="G16" s="47">
         <v>0.7</v>
       </c>
-      <c r="H16" s="57">
+      <c r="H16" s="47">
         <v>0.69</v>
       </c>
-      <c r="I16" s="57"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="46"/>
-      <c r="M16" s="46"/>
-      <c r="N16" s="46" t="s">
+      <c r="I16" s="47"/>
+      <c r="J16" s="36"/>
+      <c r="K16" s="36"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="4"/>
+      <c r="N16" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="O16" s="46" t="s">
+      <c r="O16" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="P16" s="46" t="s">
+      <c r="P16" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="Q16" s="46" t="s">
+      <c r="Q16" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="R16" s="46"/>
-      <c r="S16" s="46" t="s">
+      <c r="R16" s="4"/>
+      <c r="S16" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="T16" s="46" t="s">
+      <c r="T16" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="U16" s="46" t="s">
+      <c r="U16" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="V16" s="46" t="s">
+      <c r="V16" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="W16" s="46"/>
-      <c r="X16" s="46"/>
-      <c r="Y16" s="46" t="s">
+      <c r="W16" s="4"/>
+      <c r="X16" s="4"/>
+      <c r="Y16" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="Z16" s="46"/>
-      <c r="AA16" s="47" t="s">
+      <c r="Z16" s="4"/>
+      <c r="AA16" s="20" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="17" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A17" s="40" t="s">
+      <c r="A17" s="18" t="s">
         <v>114</v>
       </c>
-      <c r="B17" s="41" t="s">
-        <v>530</v>
-      </c>
-      <c r="C17" s="41" t="s">
+      <c r="B17" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
-      <c r="F17" s="57">
+      <c r="D17" s="47"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="47">
         <v>0.24</v>
       </c>
-      <c r="G17" s="57">
+      <c r="G17" s="47">
         <v>0.3</v>
       </c>
-      <c r="H17" s="57">
+      <c r="H17" s="47">
         <v>0.31</v>
       </c>
-      <c r="I17" s="57"/>
-      <c r="J17" s="55"/>
-      <c r="K17" s="55"/>
-      <c r="L17" s="45"/>
-      <c r="M17" s="45"/>
-      <c r="N17" s="46" t="s">
+      <c r="I17" s="47"/>
+      <c r="J17" s="37"/>
+      <c r="K17" s="37"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="17"/>
+      <c r="N17" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="O17" s="46" t="s">
+      <c r="O17" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="P17" s="46" t="s">
+      <c r="P17" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="Q17" s="46" t="s">
+      <c r="Q17" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="R17" s="46"/>
-      <c r="S17" s="46" t="s">
+      <c r="R17" s="4"/>
+      <c r="S17" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="T17" s="46" t="s">
+      <c r="T17" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="U17" s="46" t="s">
+      <c r="U17" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="V17" s="46" t="s">
+      <c r="V17" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="W17" s="46"/>
-      <c r="X17" s="46"/>
-      <c r="Y17" s="46" t="s">
+      <c r="W17" s="4"/>
+      <c r="X17" s="4"/>
+      <c r="Y17" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="Z17" s="46"/>
-      <c r="AA17" s="47" t="s">
+      <c r="Z17" s="4"/>
+      <c r="AA17" s="20" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="45" x14ac:dyDescent="0.25">
-      <c r="A18" s="40" t="s">
+      <c r="A18" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="B18" s="41" t="s">
-        <v>533</v>
-      </c>
-      <c r="C18" s="41" t="s">
+      <c r="B18" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D18" s="57">
+      <c r="D18" s="47">
         <v>0.70199999999999996</v>
       </c>
-      <c r="E18" s="57">
+      <c r="E18" s="47">
         <v>0.67</v>
       </c>
-      <c r="F18" s="57">
+      <c r="F18" s="47">
         <v>0.67300000000000004</v>
       </c>
-      <c r="G18" s="57">
+      <c r="G18" s="47">
         <v>0.71099999999999997</v>
       </c>
-      <c r="H18" s="57">
+      <c r="H18" s="47">
         <v>0.74099999999999999</v>
       </c>
-      <c r="I18" s="57">
+      <c r="I18" s="47">
         <v>0.76080000000000003</v>
       </c>
-      <c r="J18" s="55">
+      <c r="J18" s="37">
         <v>0.76080000000000003</v>
       </c>
-      <c r="K18" s="55">
+      <c r="K18" s="37">
         <v>0.8</v>
       </c>
-      <c r="L18" s="45">
+      <c r="L18" s="17">
         <v>0.74099999999999999</v>
       </c>
-      <c r="M18" s="45">
+      <c r="M18" s="17">
         <v>0.8</v>
       </c>
-      <c r="N18" s="46" t="s">
-        <v>545</v>
-      </c>
-      <c r="O18" s="46" t="s">
+      <c r="N18" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="O18" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="P18" s="46" t="s">
+      <c r="P18" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="Q18" s="46" t="s">
+      <c r="Q18" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="R18" s="46" t="s">
+      <c r="R18" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="S18" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="T18" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="U18" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="V18" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="W18" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="X18" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y18" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA18" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="S18" s="46" t="s">
+    </row>
+    <row r="19" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="47">
+        <v>0.76500000000000001</v>
+      </c>
+      <c r="I19" s="47">
+        <v>0.76100000000000001</v>
+      </c>
+      <c r="J19" s="37">
+        <v>0.76100000000000001</v>
+      </c>
+      <c r="K19" s="37">
+        <v>0.8</v>
+      </c>
+      <c r="L19" s="4"/>
+      <c r="M19" s="4"/>
+      <c r="N19" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="O19" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="P19" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q19" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="R19" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="S19" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="T18" s="46" t="s">
-        <v>124</v>
-      </c>
-      <c r="U18" s="46" t="s">
+      <c r="T19" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="U19" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="V18" s="46" t="s">
+      <c r="V19" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="W18" s="46" t="s">
-        <v>122</v>
-      </c>
-      <c r="X18" s="46" t="s">
-        <v>123</v>
-      </c>
-      <c r="Y18" s="46" t="s">
+      <c r="W19" s="4"/>
+      <c r="X19" s="4"/>
+      <c r="Y19" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="Z18" s="46" t="s">
+      <c r="Z19" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AA18" s="47" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="40" t="s">
-        <v>127</v>
-      </c>
-      <c r="B19" s="41" t="s">
-        <v>530</v>
-      </c>
-      <c r="C19" s="41" t="s">
-        <v>128</v>
-      </c>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57">
-        <v>0.76500000000000001</v>
-      </c>
-      <c r="I19" s="57">
-        <v>0.76100000000000001</v>
-      </c>
-      <c r="J19" s="55">
-        <v>0.76100000000000001</v>
-      </c>
-      <c r="K19" s="55">
-        <v>0.8</v>
-      </c>
-      <c r="L19" s="46"/>
-      <c r="M19" s="46"/>
-      <c r="N19" s="46" t="s">
-        <v>545</v>
-      </c>
-      <c r="O19" s="46" t="s">
+      <c r="AA19" s="20" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A20" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="47">
+        <v>0.75900000000000001</v>
+      </c>
+      <c r="I20" s="47"/>
+      <c r="J20" s="36"/>
+      <c r="K20" s="36"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="4"/>
+      <c r="N20" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="O20" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="P19" s="46" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q19" s="46" t="s">
+      <c r="P20" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q20" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="R19" s="46" t="s">
-        <v>125</v>
-      </c>
-      <c r="S19" s="46" t="s">
+      <c r="R20" s="4"/>
+      <c r="S20" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="T19" s="46" t="s">
-        <v>130</v>
-      </c>
-      <c r="U19" s="46" t="s">
+      <c r="T20" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="U20" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="V19" s="46" t="s">
+      <c r="V20" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="W19" s="46"/>
-      <c r="X19" s="46"/>
-      <c r="Y19" s="46" t="s">
+      <c r="W20" s="4"/>
+      <c r="X20" s="4"/>
+      <c r="Y20" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="Z19" s="46" t="s">
+      <c r="Z20" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AA19" s="47" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A20" s="40" t="s">
-        <v>132</v>
-      </c>
-      <c r="B20" s="41" t="s">
-        <v>530</v>
-      </c>
-      <c r="C20" s="41" t="s">
-        <v>133</v>
-      </c>
-      <c r="D20" s="57"/>
-      <c r="E20" s="57"/>
-      <c r="F20" s="57"/>
-      <c r="G20" s="57"/>
-      <c r="H20" s="57">
-        <v>0.75900000000000001</v>
-      </c>
-      <c r="I20" s="57"/>
-      <c r="J20" s="43"/>
-      <c r="K20" s="43"/>
-      <c r="L20" s="46"/>
-      <c r="M20" s="46"/>
-      <c r="N20" s="46" t="s">
-        <v>545</v>
-      </c>
-      <c r="O20" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="P20" s="46" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q20" s="46" t="s">
-        <v>104</v>
-      </c>
-      <c r="R20" s="46"/>
-      <c r="S20" s="46" t="s">
-        <v>95</v>
-      </c>
-      <c r="T20" s="46" t="s">
+      <c r="AA20" s="20" t="s">
         <v>134</v>
-      </c>
-      <c r="U20" s="46" t="s">
-        <v>110</v>
-      </c>
-      <c r="V20" s="46" t="s">
-        <v>111</v>
-      </c>
-      <c r="W20" s="46"/>
-      <c r="X20" s="46"/>
-      <c r="Y20" s="46" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z20" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA20" s="47" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="21" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A21" s="18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D21" s="15">
         <v>0.90300000000000002</v>
@@ -5112,10 +5082,10 @@
       <c r="L21" s="17"/>
       <c r="M21" s="17"/>
       <c r="N21" s="4" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="P21" s="4" t="s">
         <v>23</v>
@@ -5128,7 +5098,7 @@
         <v>95</v>
       </c>
       <c r="T21" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="U21" s="4"/>
       <c r="V21" s="4"/>
@@ -5141,18 +5111,18 @@
         <v>28</v>
       </c>
       <c r="AA21" s="20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="22" spans="1:27" ht="60" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="D22" s="34">
         <v>0.68100000000000005</v>
@@ -5181,25 +5151,25 @@
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
       <c r="N22" s="4" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P22" s="4" t="s">
         <v>23</v>
       </c>
       <c r="Q22" s="4" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="R22" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="S22" s="4" t="s">
         <v>95</v>
       </c>
       <c r="T22" s="4" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="U22" s="4" t="s">
         <v>93</v>
@@ -5216,18 +5186,18 @@
         <v>28</v>
       </c>
       <c r="AA22" s="20" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
     </row>
     <row r="23" spans="1:27" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="D23" s="34"/>
       <c r="E23" s="34"/>
@@ -5239,40 +5209,40 @@
       <c r="I23" s="34"/>
       <c r="J23" s="4"/>
       <c r="K23" s="4"/>
-      <c r="L23" s="51">
+      <c r="L23" s="44">
         <v>0.68</v>
       </c>
-      <c r="M23" s="51">
+      <c r="M23" s="44">
         <v>0.73</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P23" s="4" t="s">
-        <v>566</v>
+        <v>561</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="R23" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="S23" s="4" t="s">
         <v>95</v>
       </c>
       <c r="T23" s="4" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="U23" s="4"/>
       <c r="V23" s="4"/>
       <c r="W23" s="4" t="s">
-        <v>122</v>
+        <v>601</v>
       </c>
       <c r="X23" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="Y23" s="4" t="s">
         <v>98</v>
@@ -5281,87 +5251,87 @@
         <v>28</v>
       </c>
       <c r="AA23" s="20" t="s">
-        <v>568</v>
+        <v>563</v>
       </c>
     </row>
     <row r="24" spans="1:27" ht="45" x14ac:dyDescent="0.25">
-      <c r="A24" s="40" t="s">
+      <c r="A24" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="D24" s="47">
+        <v>0.73899999999999999</v>
+      </c>
+      <c r="E24" s="47">
+        <v>0.67200000000000004</v>
+      </c>
+      <c r="F24" s="47">
+        <v>0.59799999999999998</v>
+      </c>
+      <c r="G24" s="47">
+        <v>0.57799999999999996</v>
+      </c>
+      <c r="H24" s="47">
+        <v>0.59599999999999997</v>
+      </c>
+      <c r="I24" s="47">
+        <v>0.626</v>
+      </c>
+      <c r="J24" s="37">
+        <v>0.626</v>
+      </c>
+      <c r="K24" s="36"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B24" s="41" t="s">
-        <v>532</v>
-      </c>
-      <c r="C24" s="41" t="s">
+      <c r="O24" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="D24" s="57">
-        <v>0.73899999999999999</v>
-      </c>
-      <c r="E24" s="57">
-        <v>0.67200000000000004</v>
-      </c>
-      <c r="F24" s="57">
-        <v>0.59799999999999998</v>
-      </c>
-      <c r="G24" s="57">
-        <v>0.57799999999999996</v>
-      </c>
-      <c r="H24" s="57">
-        <v>0.59599999999999997</v>
-      </c>
-      <c r="I24" s="57">
-        <v>0.626</v>
-      </c>
-      <c r="J24" s="55">
-        <v>0.626</v>
-      </c>
-      <c r="K24" s="43"/>
-      <c r="L24" s="46"/>
-      <c r="M24" s="46"/>
-      <c r="N24" s="46" t="s">
-        <v>145</v>
-      </c>
-      <c r="O24" s="46" t="s">
+      <c r="P24" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="P24" s="46" t="s">
+      <c r="Q24" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="R24" s="4"/>
+      <c r="S24" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="T24" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="Q24" s="46" t="s">
+      <c r="U24" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="V24" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="W24" s="4"/>
+      <c r="X24" s="4"/>
+      <c r="Y24" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="R24" s="46"/>
-      <c r="S24" s="46" t="s">
-        <v>95</v>
-      </c>
-      <c r="T24" s="46" t="s">
-        <v>149</v>
-      </c>
-      <c r="U24" s="46" t="s">
-        <v>93</v>
-      </c>
-      <c r="V24" s="46" t="s">
-        <v>111</v>
-      </c>
-      <c r="W24" s="46"/>
-      <c r="X24" s="46"/>
-      <c r="Y24" s="46" t="s">
+      <c r="Z24" s="4"/>
+      <c r="AA24" s="20" t="s">
         <v>151</v>
-      </c>
-      <c r="Z24" s="46"/>
-      <c r="AA24" s="47" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D25" s="15"/>
       <c r="E25" s="15">
@@ -5384,23 +5354,23 @@
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
       <c r="N25" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P25" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q25" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="R25" s="4"/>
       <c r="S25" s="4" t="s">
         <v>26</v>
       </c>
       <c r="T25" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="U25" s="4"/>
       <c r="V25" s="4"/>
@@ -5411,18 +5381,18 @@
       </c>
       <c r="Z25" s="4"/>
       <c r="AA25" s="20" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" s="18" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D26" s="15">
         <v>16211</v>
@@ -5447,23 +5417,23 @@
       <c r="L26" s="17"/>
       <c r="M26" s="17"/>
       <c r="N26" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="P26" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="Q26" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="R26" s="4"/>
       <c r="S26" s="4" t="s">
         <v>26</v>
       </c>
       <c r="T26" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="U26" s="4"/>
       <c r="V26" s="4"/>
@@ -5474,288 +5444,288 @@
       </c>
       <c r="Z26" s="4"/>
       <c r="AA26" s="20" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+      <c r="A27" s="18" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="27" spans="1:27" ht="45" x14ac:dyDescent="0.25">
-      <c r="A27" s="40" t="s">
+      <c r="B27" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C27" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="B27" s="41" t="s">
-        <v>534</v>
-      </c>
-      <c r="C27" s="41" t="s">
+      <c r="D27" s="15">
+        <v>897</v>
+      </c>
+      <c r="E27" s="15">
+        <v>839</v>
+      </c>
+      <c r="F27" s="15">
+        <v>1085</v>
+      </c>
+      <c r="G27" s="15">
+        <v>1086</v>
+      </c>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="17">
+        <v>0.15</v>
+      </c>
+      <c r="M27" s="17">
+        <v>0.2</v>
+      </c>
+      <c r="N27" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="O27" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="D27" s="54">
-        <v>897</v>
-      </c>
-      <c r="E27" s="54">
-        <v>839</v>
-      </c>
-      <c r="F27" s="54">
-        <v>1085</v>
-      </c>
-      <c r="G27" s="54">
-        <v>1086</v>
-      </c>
-      <c r="H27" s="54"/>
-      <c r="I27" s="54"/>
-      <c r="J27" s="46"/>
-      <c r="K27" s="46"/>
-      <c r="L27" s="45">
-        <v>0.15</v>
-      </c>
-      <c r="M27" s="45">
-        <v>0.2</v>
-      </c>
-      <c r="N27" s="46" t="s">
-        <v>145</v>
-      </c>
-      <c r="O27" s="46" t="s">
+      <c r="P27" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="P27" s="46" t="s">
+      <c r="Q27" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="R27" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="S27" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="Q27" s="46" t="s">
+      <c r="T27" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="U27" s="4"/>
+      <c r="V27" s="4"/>
+      <c r="W27" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="X27" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="Y27" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="R27" s="46" t="s">
-        <v>535</v>
-      </c>
-      <c r="S27" s="46" t="s">
-        <v>167</v>
-      </c>
-      <c r="T27" s="46" t="s">
-        <v>168</v>
-      </c>
-      <c r="U27" s="46"/>
-      <c r="V27" s="46"/>
-      <c r="W27" s="46" t="s">
+      <c r="Z27" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA27" s="20" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+      <c r="A28" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D28" s="15">
+        <v>1874</v>
+      </c>
+      <c r="E28" s="15">
+        <v>1929</v>
+      </c>
+      <c r="F28" s="15">
+        <v>2056</v>
+      </c>
+      <c r="G28" s="15">
+        <v>2435</v>
+      </c>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="17">
+        <v>0.31</v>
+      </c>
+      <c r="M28" s="17">
+        <v>0.35</v>
+      </c>
+      <c r="N28" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="O28" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="P28" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="Q28" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="R28" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="S28" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="T28" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="U28" s="4"/>
+      <c r="V28" s="4"/>
+      <c r="W28" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="X28" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="X27" s="46" t="s">
-        <v>123</v>
-      </c>
-      <c r="Y27" s="46" t="s">
-        <v>170</v>
-      </c>
-      <c r="Z27" s="46" t="s">
+      <c r="Y28" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="Z28" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AA27" s="47" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" ht="45" x14ac:dyDescent="0.25">
-      <c r="A28" s="40" t="s">
-        <v>172</v>
-      </c>
-      <c r="B28" s="41" t="s">
-        <v>534</v>
-      </c>
-      <c r="C28" s="41" t="s">
-        <v>173</v>
-      </c>
-      <c r="D28" s="54">
-        <v>1874</v>
-      </c>
-      <c r="E28" s="54">
-        <v>1929</v>
-      </c>
-      <c r="F28" s="54">
-        <v>2056</v>
-      </c>
-      <c r="G28" s="54">
-        <v>2435</v>
-      </c>
-      <c r="H28" s="54"/>
-      <c r="I28" s="54"/>
-      <c r="J28" s="46"/>
-      <c r="K28" s="46"/>
-      <c r="L28" s="45">
-        <v>0.31</v>
-      </c>
-      <c r="M28" s="45">
-        <v>0.35</v>
-      </c>
-      <c r="N28" s="46" t="s">
-        <v>145</v>
-      </c>
-      <c r="O28" s="46" t="s">
-        <v>165</v>
-      </c>
-      <c r="P28" s="46" t="s">
-        <v>174</v>
-      </c>
-      <c r="Q28" s="46" t="s">
+      <c r="AA28" s="20" t="s">
         <v>176</v>
       </c>
-      <c r="R28" s="46" t="s">
-        <v>535</v>
-      </c>
-      <c r="S28" s="46" t="s">
-        <v>167</v>
-      </c>
-      <c r="T28" s="46" t="s">
-        <v>175</v>
-      </c>
-      <c r="U28" s="46"/>
-      <c r="V28" s="46"/>
-      <c r="W28" s="46" t="s">
-        <v>122</v>
-      </c>
-      <c r="X28" s="46" t="s">
-        <v>123</v>
-      </c>
-      <c r="Y28" s="46" t="s">
-        <v>170</v>
-      </c>
-      <c r="Z28" s="46" t="s">
+    </row>
+    <row r="29" spans="1:27" ht="75" x14ac:dyDescent="0.25">
+      <c r="A29" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="32">
+        <v>925</v>
+      </c>
+      <c r="G29" s="32">
+        <v>895</v>
+      </c>
+      <c r="H29" s="32">
+        <v>902</v>
+      </c>
+      <c r="I29" s="32"/>
+      <c r="J29" s="36"/>
+      <c r="K29" s="36"/>
+      <c r="L29" s="4"/>
+      <c r="M29" s="4"/>
+      <c r="N29" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="O29" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="P29" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="Q29" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="R29" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="S29" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="T29" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="U29" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="V29" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="W29" s="4"/>
+      <c r="X29" s="4"/>
+      <c r="Y29" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="Z29" s="4"/>
+      <c r="AA29" s="20" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="18" t="s">
+        <v>183</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="32">
+        <v>2077</v>
+      </c>
+      <c r="I30" s="15"/>
+      <c r="J30" s="4"/>
+      <c r="K30" s="4"/>
+      <c r="L30" s="4">
+        <v>2077</v>
+      </c>
+      <c r="M30" s="4">
+        <v>3264</v>
+      </c>
+      <c r="N30" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="O30" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="P30" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q30" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="R30" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="S30" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="T30" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="U30" s="4"/>
+      <c r="V30" s="4"/>
+      <c r="W30" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="X30" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="Y30" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z30" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="AA28" s="47" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="29" spans="1:27" ht="75" x14ac:dyDescent="0.25">
-      <c r="A29" s="40" t="s">
-        <v>178</v>
-      </c>
-      <c r="B29" s="41" t="s">
-        <v>532</v>
-      </c>
-      <c r="C29" s="41" t="s">
-        <v>179</v>
-      </c>
-      <c r="D29" s="48"/>
-      <c r="E29" s="48"/>
-      <c r="F29" s="48">
-        <v>925</v>
-      </c>
-      <c r="G29" s="48">
-        <v>895</v>
-      </c>
-      <c r="H29" s="48">
-        <v>902</v>
-      </c>
-      <c r="I29" s="48"/>
-      <c r="J29" s="43"/>
-      <c r="K29" s="43"/>
-      <c r="L29" s="46"/>
-      <c r="M29" s="46"/>
-      <c r="N29" s="46" t="s">
-        <v>145</v>
-      </c>
-      <c r="O29" s="46" t="s">
-        <v>165</v>
-      </c>
-      <c r="P29" s="46" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q29" s="46" t="s">
-        <v>182</v>
-      </c>
-      <c r="R29" s="46" t="s">
-        <v>42</v>
-      </c>
-      <c r="S29" s="46" t="s">
-        <v>26</v>
-      </c>
-      <c r="T29" s="46" t="s">
-        <v>181</v>
-      </c>
-      <c r="U29" s="46" t="s">
-        <v>110</v>
-      </c>
-      <c r="V29" s="46" t="s">
-        <v>111</v>
-      </c>
-      <c r="W29" s="46"/>
-      <c r="X29" s="46"/>
-      <c r="Y29" s="46" t="s">
-        <v>170</v>
-      </c>
-      <c r="Z29" s="46"/>
-      <c r="AA29" s="47" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="40" t="s">
-        <v>184</v>
-      </c>
-      <c r="B30" s="41" t="s">
-        <v>189</v>
-      </c>
-      <c r="C30" s="41" t="s">
-        <v>186</v>
-      </c>
-      <c r="D30" s="54"/>
-      <c r="E30" s="54"/>
-      <c r="F30" s="54"/>
-      <c r="G30" s="54"/>
-      <c r="H30" s="48">
-        <v>2077</v>
-      </c>
-      <c r="I30" s="54"/>
-      <c r="J30" s="46"/>
-      <c r="K30" s="46"/>
-      <c r="L30" s="46">
-        <v>2077</v>
-      </c>
-      <c r="M30" s="46">
-        <v>3264</v>
-      </c>
-      <c r="N30" s="46" t="s">
-        <v>185</v>
-      </c>
-      <c r="O30" s="46" t="s">
-        <v>187</v>
-      </c>
-      <c r="P30" s="46" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q30" s="46" t="s">
-        <v>193</v>
-      </c>
-      <c r="R30" s="46" t="s">
-        <v>536</v>
-      </c>
-      <c r="S30" s="46" t="s">
-        <v>191</v>
-      </c>
-      <c r="T30" s="46" t="s">
-        <v>192</v>
-      </c>
-      <c r="U30" s="46"/>
-      <c r="V30" s="46"/>
-      <c r="W30" s="46" t="s">
-        <v>122</v>
-      </c>
-      <c r="X30" s="46" t="s">
-        <v>190</v>
-      </c>
-      <c r="Y30" s="46" t="s">
+      <c r="AA30" s="20" t="s">
         <v>194</v>
-      </c>
-      <c r="Z30" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA30" s="47" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="31" spans="1:27" ht="60" x14ac:dyDescent="0.25">
       <c r="A31" s="19" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="D31" s="33">
         <v>1283</v>
@@ -5778,53 +5748,53 @@
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
       <c r="N31" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P31" s="4" t="s">
-        <v>570</v>
+        <v>565</v>
       </c>
       <c r="Q31" s="4" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="R31" s="4" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="S31" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="T31" s="4" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="U31" s="4" t="s">
         <v>93</v>
       </c>
       <c r="V31" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="W31" s="4"/>
       <c r="X31" s="4"/>
       <c r="Y31" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Z31" s="4" t="s">
         <v>28</v>
       </c>
       <c r="AA31" s="20" t="s">
-        <v>572</v>
+        <v>567</v>
       </c>
     </row>
     <row r="32" spans="1:27" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>599</v>
+        <v>594</v>
       </c>
       <c r="D32" s="16"/>
       <c r="E32" s="16"/>
@@ -5843,122 +5813,122 @@
         <v>1620</v>
       </c>
       <c r="N32" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P32" s="4" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="Q32" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R32" s="4" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="S32" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="T32" s="4" t="s">
-        <v>575</v>
+        <v>570</v>
       </c>
       <c r="U32" s="4"/>
       <c r="V32" s="4"/>
       <c r="W32" s="4" t="s">
-        <v>122</v>
+        <v>601</v>
       </c>
       <c r="X32" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Y32" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Z32" s="4" t="s">
         <v>28</v>
       </c>
       <c r="AA32" s="20" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
     </row>
     <row r="33" spans="1:27" ht="45" x14ac:dyDescent="0.25">
-      <c r="A33" s="40" t="s">
+      <c r="A33" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="B33" s="41" t="s">
+      <c r="D33" s="32">
+        <v>812</v>
+      </c>
+      <c r="E33" s="32">
+        <v>728</v>
+      </c>
+      <c r="F33" s="32">
+        <v>573</v>
+      </c>
+      <c r="G33" s="32">
+        <v>523</v>
+      </c>
+      <c r="H33" s="32">
+        <v>544</v>
+      </c>
+      <c r="I33" s="32"/>
+      <c r="J33" s="36"/>
+      <c r="K33" s="36"/>
+      <c r="L33" s="4"/>
+      <c r="M33" s="4"/>
+      <c r="N33" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="O33" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="P33" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="Q33" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="R33" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="C33" s="41" t="s">
-        <v>198</v>
-      </c>
-      <c r="D33" s="48">
-        <v>812</v>
-      </c>
-      <c r="E33" s="48">
-        <v>728</v>
-      </c>
-      <c r="F33" s="48">
-        <v>573</v>
-      </c>
-      <c r="G33" s="48">
-        <v>523</v>
-      </c>
-      <c r="H33" s="48">
-        <v>544</v>
-      </c>
-      <c r="I33" s="48"/>
-      <c r="J33" s="43"/>
-      <c r="K33" s="43"/>
-      <c r="L33" s="46"/>
-      <c r="M33" s="46"/>
-      <c r="N33" s="46" t="s">
-        <v>185</v>
-      </c>
-      <c r="O33" s="46" t="s">
-        <v>187</v>
-      </c>
-      <c r="P33" s="46" t="s">
+      <c r="S33" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="T33" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="Q33" s="46" t="s">
-        <v>77</v>
-      </c>
-      <c r="R33" s="46" t="s">
-        <v>537</v>
-      </c>
-      <c r="S33" s="46" t="s">
-        <v>191</v>
-      </c>
-      <c r="T33" s="46" t="s">
+      <c r="U33" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="V33" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="W33" s="4"/>
+      <c r="X33" s="4"/>
+      <c r="Y33" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z33" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA33" s="20" t="s">
         <v>200</v>
-      </c>
-      <c r="U33" s="46" t="s">
-        <v>93</v>
-      </c>
-      <c r="V33" s="46" t="s">
-        <v>196</v>
-      </c>
-      <c r="W33" s="46"/>
-      <c r="X33" s="46"/>
-      <c r="Y33" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="Z33" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA33" s="47" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="34" spans="1:27" ht="60" x14ac:dyDescent="0.25">
       <c r="A34" s="19" t="s">
-        <v>577</v>
+        <v>572</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
       <c r="D34" s="33">
         <v>187</v>
@@ -5981,53 +5951,53 @@
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
       <c r="N34" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P34" s="4" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="Q34" s="4" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="R34" s="4" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="S34" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="T34" s="4" t="s">
-        <v>579</v>
+        <v>574</v>
       </c>
       <c r="U34" s="4" t="s">
         <v>93</v>
       </c>
       <c r="V34" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="W34" s="4"/>
       <c r="X34" s="4"/>
       <c r="Y34" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Z34" s="4" t="s">
         <v>28</v>
       </c>
       <c r="AA34" s="20" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
     </row>
     <row r="35" spans="1:27" ht="60" x14ac:dyDescent="0.25">
       <c r="A35" s="19" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="D35" s="16"/>
       <c r="E35" s="16"/>
@@ -6046,258 +6016,258 @@
         <v>1200</v>
       </c>
       <c r="N35" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="O35" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="P35" s="4" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="Q35" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="R35" s="4" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="S35" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="T35" s="4" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="U35" s="4"/>
       <c r="V35" s="4"/>
       <c r="W35" s="4" t="s">
-        <v>122</v>
+        <v>601</v>
       </c>
       <c r="X35" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Y35" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Z35" s="4" t="s">
         <v>28</v>
       </c>
       <c r="AA35" s="20" t="s">
-        <v>584</v>
+        <v>579</v>
       </c>
     </row>
     <row r="36" spans="1:27" ht="75" x14ac:dyDescent="0.25">
-      <c r="A36" s="40" t="s">
+      <c r="A36" s="18" t="s">
+        <v>201</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="C36" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="B36" s="41" t="s">
+      <c r="D36" s="40"/>
+      <c r="E36" s="40"/>
+      <c r="F36" s="40">
+        <v>83.8</v>
+      </c>
+      <c r="G36" s="40">
+        <v>86.5</v>
+      </c>
+      <c r="H36" s="40">
+        <v>81</v>
+      </c>
+      <c r="I36" s="40"/>
+      <c r="J36" s="36"/>
+      <c r="K36" s="36"/>
+      <c r="L36" s="41">
+        <v>81</v>
+      </c>
+      <c r="M36" s="41">
+        <v>76</v>
+      </c>
+      <c r="N36" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="O36" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="P36" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q36" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="R36" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="S36" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="T36" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="U36" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="V36" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="W36" s="4" t="s">
+        <v>601</v>
+      </c>
+      <c r="X36" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="Y36" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z36" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA36" s="20" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" ht="60" x14ac:dyDescent="0.25">
+      <c r="A37" s="18" t="s">
+        <v>209</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D37" s="40"/>
+      <c r="E37" s="40">
+        <v>83</v>
+      </c>
+      <c r="F37" s="40">
+        <v>81</v>
+      </c>
+      <c r="G37" s="40">
+        <v>79</v>
+      </c>
+      <c r="H37" s="40">
+        <v>79</v>
+      </c>
+      <c r="I37" s="40"/>
+      <c r="J37" s="36"/>
+      <c r="K37" s="36">
+        <v>77</v>
+      </c>
+      <c r="L37" s="17"/>
+      <c r="M37" s="17"/>
+      <c r="N37" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="O37" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="P37" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="Q37" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="R37" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="C36" s="41" t="s">
+      <c r="S37" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="T37" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="U37" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="V37" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="W37" s="4"/>
+      <c r="X37" s="4"/>
+      <c r="Y37" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z37" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA37" s="20" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" ht="45" x14ac:dyDescent="0.25">
+      <c r="A38" s="18" t="s">
+        <v>215</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="D38" s="40"/>
+      <c r="E38" s="40"/>
+      <c r="F38" s="40">
+        <v>87.6</v>
+      </c>
+      <c r="G38" s="40">
+        <v>87</v>
+      </c>
+      <c r="H38" s="40">
+        <v>89.4</v>
+      </c>
+      <c r="I38" s="40"/>
+      <c r="J38" s="36"/>
+      <c r="K38" s="36">
+        <v>79</v>
+      </c>
+      <c r="L38" s="17"/>
+      <c r="M38" s="17"/>
+      <c r="N38" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="O38" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="D36" s="42"/>
-      <c r="E36" s="42"/>
-      <c r="F36" s="42">
-        <v>83.8</v>
-      </c>
-      <c r="G36" s="42">
-        <v>86.5</v>
-      </c>
-      <c r="H36" s="42">
-        <v>81</v>
-      </c>
-      <c r="I36" s="42"/>
-      <c r="J36" s="43"/>
-      <c r="K36" s="43"/>
-      <c r="L36" s="44">
-        <v>81</v>
-      </c>
-      <c r="M36" s="44">
-        <v>76</v>
-      </c>
-      <c r="N36" s="46" t="s">
-        <v>185</v>
-      </c>
-      <c r="O36" s="46" t="s">
-        <v>204</v>
-      </c>
-      <c r="P36" s="46" t="s">
+      <c r="P38" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="Q38" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="R38" s="4"/>
+      <c r="S38" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="Q36" s="46" t="s">
-        <v>208</v>
-      </c>
-      <c r="R36" s="46" t="s">
-        <v>536</v>
-      </c>
-      <c r="S36" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="T36" s="46" t="s">
-        <v>207</v>
-      </c>
-      <c r="U36" s="46" t="s">
+      <c r="T38" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="U38" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="V36" s="46" t="s">
-        <v>196</v>
-      </c>
-      <c r="W36" s="46" t="s">
-        <v>122</v>
-      </c>
-      <c r="X36" s="46" t="s">
-        <v>142</v>
-      </c>
-      <c r="Y36" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="Z36" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA36" s="47" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="37" spans="1:27" ht="60" x14ac:dyDescent="0.25">
-      <c r="A37" s="40" t="s">
-        <v>210</v>
-      </c>
-      <c r="B37" s="41" t="s">
-        <v>532</v>
-      </c>
-      <c r="C37" s="41" t="s">
-        <v>211</v>
-      </c>
-      <c r="D37" s="42"/>
-      <c r="E37" s="42">
-        <v>83</v>
-      </c>
-      <c r="F37" s="42">
-        <v>81</v>
-      </c>
-      <c r="G37" s="42">
-        <v>79</v>
-      </c>
-      <c r="H37" s="42">
-        <v>79</v>
-      </c>
-      <c r="I37" s="42"/>
-      <c r="J37" s="43"/>
-      <c r="K37" s="43">
-        <v>77</v>
-      </c>
-      <c r="L37" s="45"/>
-      <c r="M37" s="45"/>
-      <c r="N37" s="46" t="s">
-        <v>185</v>
-      </c>
-      <c r="O37" s="46" t="s">
-        <v>204</v>
-      </c>
-      <c r="P37" s="46" t="s">
-        <v>212</v>
-      </c>
-      <c r="Q37" s="46" t="s">
-        <v>214</v>
-      </c>
-      <c r="R37" s="46" t="s">
-        <v>538</v>
-      </c>
-      <c r="S37" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="T37" s="46" t="s">
-        <v>213</v>
-      </c>
-      <c r="U37" s="46" t="s">
-        <v>93</v>
-      </c>
-      <c r="V37" s="46" t="s">
-        <v>196</v>
-      </c>
-      <c r="W37" s="46"/>
-      <c r="X37" s="46"/>
-      <c r="Y37" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="Z37" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA37" s="47" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="38" spans="1:27" ht="45" x14ac:dyDescent="0.25">
-      <c r="A38" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="B38" s="41" t="s">
-        <v>530</v>
-      </c>
-      <c r="C38" s="41" t="s">
-        <v>217</v>
-      </c>
-      <c r="D38" s="42"/>
-      <c r="E38" s="42"/>
-      <c r="F38" s="42">
-        <v>87.6</v>
-      </c>
-      <c r="G38" s="42">
-        <v>87</v>
-      </c>
-      <c r="H38" s="42">
-        <v>89.4</v>
-      </c>
-      <c r="I38" s="42"/>
-      <c r="J38" s="43"/>
-      <c r="K38" s="43">
-        <v>79</v>
-      </c>
-      <c r="L38" s="45"/>
-      <c r="M38" s="45"/>
-      <c r="N38" s="46" t="s">
-        <v>185</v>
-      </c>
-      <c r="O38" s="46" t="s">
-        <v>204</v>
-      </c>
-      <c r="P38" s="46" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q38" s="46" t="s">
-        <v>214</v>
-      </c>
-      <c r="R38" s="46"/>
-      <c r="S38" s="46" t="s">
-        <v>206</v>
-      </c>
-      <c r="T38" s="46" t="s">
+      <c r="V38" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="W38" s="4"/>
+      <c r="X38" s="4"/>
+      <c r="Y38" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z38" s="4"/>
+      <c r="AA38" s="20" t="s">
         <v>219</v>
-      </c>
-      <c r="U38" s="46" t="s">
-        <v>93</v>
-      </c>
-      <c r="V38" s="46" t="s">
-        <v>196</v>
-      </c>
-      <c r="W38" s="46"/>
-      <c r="X38" s="46"/>
-      <c r="Y38" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="Z38" s="46"/>
-      <c r="AA38" s="47" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="39" spans="1:27" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="19" t="s">
-        <v>585</v>
+        <v>580</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="D39" s="33">
         <v>1062</v>
@@ -6320,53 +6290,53 @@
       <c r="L39" s="17"/>
       <c r="M39" s="17"/>
       <c r="N39" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="O39" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="O39" s="4" t="s">
-        <v>222</v>
-      </c>
       <c r="P39" s="4" t="s">
-        <v>586</v>
+        <v>581</v>
       </c>
       <c r="Q39" s="4" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="R39" s="4" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="S39" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="T39" s="4" t="s">
-        <v>587</v>
+        <v>582</v>
       </c>
       <c r="U39" s="4" t="s">
         <v>93</v>
       </c>
       <c r="V39" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="W39" s="4"/>
       <c r="X39" s="4"/>
       <c r="Y39" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Z39" s="4" t="s">
         <v>28</v>
       </c>
       <c r="AA39" s="20" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
     </row>
     <row r="40" spans="1:27" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="19" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="D40" s="16"/>
       <c r="E40" s="16"/>
@@ -6378,137 +6348,137 @@
       <c r="I40" s="16"/>
       <c r="J40" s="4"/>
       <c r="K40" s="4"/>
-      <c r="L40" s="50">
+      <c r="L40" s="43">
         <v>2010</v>
       </c>
-      <c r="M40" s="50">
+      <c r="M40" s="43">
         <v>2300</v>
       </c>
       <c r="N40" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="O40" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="O40" s="4" t="s">
-        <v>222</v>
-      </c>
       <c r="P40" s="4" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="Q40" s="4" t="s">
-        <v>591</v>
+        <v>586</v>
       </c>
       <c r="R40" s="4" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="S40" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="T40" s="4" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="U40" s="4"/>
       <c r="V40" s="4"/>
       <c r="W40" s="4" t="s">
-        <v>223</v>
+        <v>602</v>
       </c>
       <c r="X40" s="4" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="Y40" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Z40" s="4" t="s">
         <v>28</v>
       </c>
       <c r="AA40" s="20" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="41" spans="1:27" ht="75" x14ac:dyDescent="0.25">
+      <c r="A41" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="D41" s="32">
+        <v>2648</v>
+      </c>
+      <c r="E41" s="32">
+        <v>2657</v>
+      </c>
+      <c r="F41" s="32">
+        <v>2821</v>
+      </c>
+      <c r="G41" s="32">
+        <v>3212</v>
+      </c>
+      <c r="H41" s="32">
+        <v>3912</v>
+      </c>
+      <c r="I41" s="32"/>
+      <c r="J41" s="36"/>
+      <c r="K41" s="36"/>
+      <c r="L41" s="44">
+        <v>0.13</v>
+      </c>
+      <c r="M41" s="44">
+        <v>0.18</v>
+      </c>
+      <c r="N41" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="O41" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="P41" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q41" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="R41" s="4" t="s">
+        <v>534</v>
+      </c>
+      <c r="S41" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="T41" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="U41" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="V41" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="W41" s="4" t="s">
         <v>604</v>
       </c>
-    </row>
-    <row r="41" spans="1:27" ht="75" x14ac:dyDescent="0.25">
-      <c r="A41" s="40" t="s">
-        <v>225</v>
-      </c>
-      <c r="B41" s="41" t="s">
-        <v>533</v>
-      </c>
-      <c r="C41" s="41" t="s">
+      <c r="X41" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="D41" s="48">
-        <v>2648</v>
-      </c>
-      <c r="E41" s="48">
-        <v>2657</v>
-      </c>
-      <c r="F41" s="48">
-        <v>2821</v>
-      </c>
-      <c r="G41" s="48">
-        <v>3212</v>
-      </c>
-      <c r="H41" s="48">
-        <v>3912</v>
-      </c>
-      <c r="I41" s="48"/>
-      <c r="J41" s="43"/>
-      <c r="K41" s="43"/>
-      <c r="L41" s="52">
-        <v>0.13</v>
-      </c>
-      <c r="M41" s="52">
-        <v>0.18</v>
-      </c>
-      <c r="N41" s="46" t="s">
-        <v>226</v>
-      </c>
-      <c r="O41" s="46" t="s">
-        <v>228</v>
-      </c>
-      <c r="P41" s="46" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q41" s="46" t="s">
-        <v>233</v>
-      </c>
-      <c r="R41" s="46" t="s">
-        <v>539</v>
-      </c>
-      <c r="S41" s="46" t="s">
+      <c r="Y41" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z41" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA41" s="20" t="s">
         <v>231</v>
-      </c>
-      <c r="T41" s="46" t="s">
-        <v>232</v>
-      </c>
-      <c r="U41" s="46" t="s">
-        <v>93</v>
-      </c>
-      <c r="V41" s="46" t="s">
-        <v>196</v>
-      </c>
-      <c r="W41" s="46" t="s">
-        <v>229</v>
-      </c>
-      <c r="X41" s="46" t="s">
-        <v>230</v>
-      </c>
-      <c r="Y41" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="Z41" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA41" s="47" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="42" spans="1:27" ht="60" x14ac:dyDescent="0.25">
       <c r="A42" s="18" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D42" s="32">
         <v>3346</v>
@@ -6533,342 +6503,342 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="N42" s="4" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="O42" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="P42" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q42" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="P42" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="Q42" s="4" t="s">
-        <v>240</v>
-      </c>
       <c r="R42" s="4" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="S42" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="T42" s="4" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="U42" s="4"/>
       <c r="V42" s="4"/>
       <c r="W42" s="4" t="s">
-        <v>229</v>
+        <v>604</v>
       </c>
       <c r="X42" s="4" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="Y42" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="Z42" s="4" t="s">
         <v>28</v>
       </c>
       <c r="AA42" s="20" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="43" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A43" s="18" t="s">
+        <v>239</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D43" s="15"/>
+      <c r="E43" s="15"/>
+      <c r="F43" s="15"/>
+      <c r="G43" s="15"/>
+      <c r="H43" s="15"/>
+      <c r="I43" s="48">
+        <v>0.71</v>
+      </c>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4"/>
+      <c r="L43" s="44">
+        <v>0.71</v>
+      </c>
+      <c r="M43" s="44">
+        <v>0.8</v>
+      </c>
+      <c r="N43" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="O43" s="4" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="43" spans="1:27" ht="30" x14ac:dyDescent="0.25">
-      <c r="A43" s="40" t="s">
+      <c r="P43" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="B43" s="41" t="s">
-        <v>189</v>
-      </c>
-      <c r="C43" s="41" t="s">
+      <c r="Q43" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="R43" s="4"/>
+      <c r="S43" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="T43" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="U43" s="4"/>
+      <c r="V43" s="4"/>
+      <c r="W43" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="X43" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="D43" s="54"/>
-      <c r="E43" s="54"/>
-      <c r="F43" s="54"/>
-      <c r="G43" s="54"/>
-      <c r="H43" s="54"/>
-      <c r="I43" s="58">
-        <v>0.71</v>
-      </c>
-      <c r="J43" s="46"/>
-      <c r="K43" s="46"/>
-      <c r="L43" s="52">
-        <v>0.71</v>
-      </c>
-      <c r="M43" s="52">
-        <v>0.8</v>
-      </c>
-      <c r="N43" s="46" t="s">
-        <v>546</v>
-      </c>
-      <c r="O43" s="46" t="s">
-        <v>244</v>
-      </c>
-      <c r="P43" s="46" t="s">
+      <c r="Y43" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z43" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="Q43" s="46" t="s">
+      <c r="AA43" s="20" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A44" s="18" t="s">
+        <v>248</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D44" s="48"/>
+      <c r="E44" s="48"/>
+      <c r="F44" s="48"/>
+      <c r="G44" s="48"/>
+      <c r="H44" s="47">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="I44" s="48"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="17">
+        <v>0.29499999999999998</v>
+      </c>
+      <c r="M44" s="17">
+        <v>0.35</v>
+      </c>
+      <c r="N44" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="O44" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="R43" s="46"/>
-      <c r="S43" s="46" t="s">
+      <c r="P44" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q44" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="R44" s="4"/>
+      <c r="S44" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="T43" s="46" t="s">
-        <v>248</v>
-      </c>
-      <c r="U43" s="46"/>
-      <c r="V43" s="46"/>
-      <c r="W43" s="46" t="s">
-        <v>246</v>
-      </c>
-      <c r="X43" s="46" t="s">
-        <v>247</v>
-      </c>
-      <c r="Y43" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="Z43" s="46" t="s">
-        <v>249</v>
-      </c>
-      <c r="AA43" s="47" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A44" s="40" t="s">
+      <c r="T44" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="U44" s="4"/>
+      <c r="V44" s="4"/>
+      <c r="W44" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="X44" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="B44" s="41" t="s">
-        <v>189</v>
-      </c>
-      <c r="C44" s="41" t="s">
-        <v>253</v>
-      </c>
-      <c r="D44" s="58"/>
-      <c r="E44" s="58"/>
-      <c r="F44" s="58"/>
-      <c r="G44" s="58"/>
-      <c r="H44" s="57">
-        <v>0.29499999999999998</v>
-      </c>
-      <c r="I44" s="58"/>
-      <c r="J44" s="46"/>
-      <c r="K44" s="46"/>
-      <c r="L44" s="45">
-        <v>0.29499999999999998</v>
-      </c>
-      <c r="M44" s="45">
-        <v>0.35</v>
-      </c>
-      <c r="N44" s="46" t="s">
-        <v>546</v>
-      </c>
-      <c r="O44" s="46" t="s">
-        <v>254</v>
-      </c>
-      <c r="P44" s="46" t="s">
+      <c r="Y44" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z44" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AA44" s="20" t="s">
         <v>255</v>
       </c>
-      <c r="Q44" s="46" t="s">
+    </row>
+    <row r="45" spans="1:27" ht="30" x14ac:dyDescent="0.25">
+      <c r="A45" s="18" t="s">
+        <v>256</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="D45" s="48"/>
+      <c r="E45" s="48"/>
+      <c r="F45" s="48"/>
+      <c r="G45" s="48"/>
+      <c r="H45" s="48">
+        <v>0.49</v>
+      </c>
+      <c r="I45" s="48"/>
+      <c r="J45" s="4"/>
+      <c r="K45" s="4"/>
+      <c r="L45" s="44">
+        <v>0.49</v>
+      </c>
+      <c r="M45" s="44">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="N45" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="O45" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="P45" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="R44" s="46"/>
-      <c r="S44" s="46" t="s">
+      <c r="Q45" s="4"/>
+      <c r="R45" s="4"/>
+      <c r="S45" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="T44" s="46" t="s">
-        <v>257</v>
-      </c>
-      <c r="U44" s="46"/>
-      <c r="V44" s="46"/>
-      <c r="W44" s="46" t="s">
-        <v>246</v>
-      </c>
-      <c r="X44" s="46" t="s">
-        <v>256</v>
-      </c>
-      <c r="Y44" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="Z44" s="46" t="s">
-        <v>28</v>
-      </c>
-      <c r="AA44" s="47" t="s">
+      <c r="T45" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="U45" s="4"/>
+      <c r="V45" s="4"/>
+      <c r="W45" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="X45" s="4" t="s">
         <v>259</v>
       </c>
-    </row>
-    <row r="45" spans="1:27" ht="30" x14ac:dyDescent="0.25">
-      <c r="A45" s="40" t="s">
-        <v>260</v>
-      </c>
-      <c r="B45" s="41" t="s">
-        <v>189</v>
-      </c>
-      <c r="C45" s="41" t="s">
+      <c r="Y45" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z45" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="D45" s="58"/>
-      <c r="E45" s="58"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="58"/>
-      <c r="H45" s="58">
-        <v>0.49</v>
-      </c>
-      <c r="I45" s="58"/>
-      <c r="J45" s="46"/>
-      <c r="K45" s="46"/>
-      <c r="L45" s="52">
-        <v>0.49</v>
-      </c>
-      <c r="M45" s="52">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="N45" s="46" t="s">
-        <v>546</v>
-      </c>
-      <c r="O45" s="46" t="s">
-        <v>254</v>
-      </c>
-      <c r="P45" s="46" t="s">
+      <c r="AA45" s="20" t="s">
         <v>262</v>
       </c>
-      <c r="Q45" s="46"/>
-      <c r="R45" s="46"/>
-      <c r="S45" s="46" t="s">
-        <v>95</v>
-      </c>
-      <c r="T45" s="46" t="s">
+    </row>
+    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A46" s="18" t="s">
+        <v>263</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C46" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="U45" s="46"/>
-      <c r="V45" s="46"/>
-      <c r="W45" s="46" t="s">
-        <v>246</v>
-      </c>
-      <c r="X45" s="46" t="s">
-        <v>263</v>
-      </c>
-      <c r="Y45" s="46" t="s">
-        <v>194</v>
-      </c>
-      <c r="Z45" s="46" t="s">
+      <c r="D46" s="32"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32">
+        <v>6859</v>
+      </c>
+      <c r="I46" s="32"/>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4"/>
+      <c r="L46" s="4">
+        <v>6859</v>
+      </c>
+      <c r="M46" s="4"/>
+      <c r="N46" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="O46" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="AA45" s="47" t="s">
+      <c r="P46" s="4" t="s">
         <v>266</v>
       </c>
-    </row>
-    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A46" s="40" t="s">
+      <c r="Q46" s="4"/>
+      <c r="R46" s="4"/>
+      <c r="S46" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="B46" s="41" t="s">
-        <v>189</v>
-      </c>
-      <c r="C46" s="41" t="s">
+      <c r="T46" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="D46" s="48"/>
-      <c r="E46" s="48"/>
-      <c r="F46" s="48"/>
-      <c r="G46" s="48"/>
-      <c r="H46" s="48">
-        <v>6859</v>
-      </c>
-      <c r="I46" s="48"/>
-      <c r="J46" s="46"/>
-      <c r="K46" s="46"/>
-      <c r="L46" s="46">
-        <v>6859</v>
-      </c>
-      <c r="M46" s="46"/>
-      <c r="N46" s="46" t="s">
-        <v>546</v>
-      </c>
-      <c r="O46" s="46" t="s">
-        <v>269</v>
-      </c>
-      <c r="P46" s="46" t="s">
-        <v>270</v>
-      </c>
-      <c r="Q46" s="46"/>
-      <c r="R46" s="46"/>
-      <c r="S46" s="46" t="s">
-        <v>271</v>
-      </c>
-      <c r="T46" s="46" t="s">
-        <v>272</v>
-      </c>
-      <c r="U46" s="46"/>
-      <c r="V46" s="46"/>
-      <c r="W46" s="46" t="s">
-        <v>246</v>
-      </c>
-      <c r="X46" s="46" t="s">
-        <v>263</v>
-      </c>
-      <c r="Y46" s="46" t="s">
-        <v>170</v>
-      </c>
-      <c r="Z46" s="46" t="s">
-        <v>265</v>
-      </c>
-      <c r="AA46" s="47" t="s">
+      <c r="U46" s="4"/>
+      <c r="V46" s="4"/>
+      <c r="W46" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="X46" s="4" t="s">
         <v>259</v>
+      </c>
+      <c r="Y46" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="Z46" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="AA46" s="20" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="47" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A47" s="18" t="s">
+        <v>269</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="B47" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="D47" s="49"/>
-      <c r="E47" s="49"/>
-      <c r="F47" s="49"/>
-      <c r="G47" s="49"/>
-      <c r="H47" s="49">
+      <c r="D47" s="42"/>
+      <c r="E47" s="42"/>
+      <c r="F47" s="42"/>
+      <c r="G47" s="42"/>
+      <c r="H47" s="42">
         <v>0.71299999999999997</v>
       </c>
-      <c r="I47" s="49"/>
+      <c r="I47" s="42"/>
       <c r="J47" s="4"/>
       <c r="K47" s="4"/>
       <c r="L47" s="4" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="M47" s="17">
         <v>0.75</v>
       </c>
       <c r="N47" s="4" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="P47" s="4" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="Q47" s="4" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="R47" s="4"/>
       <c r="S47" s="4" t="s">
         <v>95</v>
       </c>
       <c r="T47" s="4" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="U47" s="4"/>
       <c r="V47" s="4"/>
       <c r="W47" s="4" t="s">
-        <v>276</v>
+        <v>605</v>
       </c>
       <c r="X47" s="4" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="Y47" s="4" t="s">
         <v>98</v>
@@ -6877,18 +6847,18 @@
         <v>28</v>
       </c>
       <c r="AA47" s="20" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
     </row>
     <row r="48" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A48" s="18" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="D48" s="32">
         <v>20704</v>
@@ -6913,13 +6883,13 @@
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
       <c r="N48" s="4" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="P48" s="4" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="Q48" s="4" t="s">
         <v>29</v>
@@ -6929,7 +6899,7 @@
         <v>26</v>
       </c>
       <c r="T48" s="4" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="U48" s="4"/>
       <c r="V48" s="4"/>
@@ -6943,13 +6913,13 @@
     </row>
     <row r="49" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A49" s="18" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="D49" s="32">
         <v>5677</v>
@@ -6974,13 +6944,13 @@
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
       <c r="N49" s="4" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="O49" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="P49" s="4" t="s">
         <v>294</v>
-      </c>
-      <c r="P49" s="4" t="s">
-        <v>299</v>
       </c>
       <c r="Q49" s="4" t="s">
         <v>29</v>
@@ -6990,7 +6960,7 @@
         <v>26</v>
       </c>
       <c r="T49" s="4" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="U49" s="4"/>
       <c r="V49" s="4"/>
@@ -7004,13 +6974,13 @@
     </row>
     <row r="50" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A50" s="18" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="D50" s="32">
         <v>14721</v>
@@ -7035,13 +7005,13 @@
       <c r="L50" s="4"/>
       <c r="M50" s="4"/>
       <c r="N50" s="4" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="O50" s="4" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="P50" s="4" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="Q50" s="4" t="s">
         <v>29</v>
@@ -7051,7 +7021,7 @@
         <v>26</v>
       </c>
       <c r="T50" s="4" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="U50" s="4"/>
       <c r="V50" s="4"/>
@@ -7065,13 +7035,13 @@
     </row>
     <row r="51" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A51" s="18" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="D51" s="32">
         <v>306</v>
@@ -7096,13 +7066,13 @@
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
       <c r="N51" s="4" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="O51" s="4" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="P51" s="4" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="Q51" s="4" t="s">
         <v>29</v>
@@ -7112,7 +7082,7 @@
         <v>26</v>
       </c>
       <c r="T51" s="4" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="U51" s="4"/>
       <c r="V51" s="4"/>
@@ -7126,13 +7096,13 @@
     </row>
     <row r="52" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A52" s="18" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>310</v>
+        <v>305</v>
       </c>
       <c r="D52" s="32">
         <v>18679</v>
@@ -7157,13 +7127,13 @@
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
       <c r="N52" s="4" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="O52" s="4" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="P52" s="4" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="Q52" s="4" t="s">
         <v>29</v>
@@ -7173,7 +7143,7 @@
         <v>26</v>
       </c>
       <c r="T52" s="4" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="U52" s="4"/>
       <c r="V52" s="4"/>
@@ -7187,13 +7157,13 @@
     </row>
     <row r="53" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A53" s="18" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="D53" s="32">
         <v>4633</v>
@@ -7218,13 +7188,13 @@
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
       <c r="N53" s="4" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="O53" s="4" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="P53" s="4" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="Q53" s="4" t="s">
         <v>29</v>
@@ -7234,7 +7204,7 @@
         <v>26</v>
       </c>
       <c r="T53" s="4" t="s">
-        <v>316</v>
+        <v>311</v>
       </c>
       <c r="U53" s="4"/>
       <c r="V53" s="4"/>
@@ -7248,13 +7218,13 @@
     </row>
     <row r="54" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A54" s="18" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="D54" s="32">
         <v>13733</v>
@@ -7279,13 +7249,13 @@
       <c r="L54" s="4"/>
       <c r="M54" s="4"/>
       <c r="N54" s="4" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="P54" s="4" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="Q54" s="4" t="s">
         <v>29</v>
@@ -7295,7 +7265,7 @@
         <v>26</v>
       </c>
       <c r="T54" s="4" t="s">
-        <v>320</v>
+        <v>315</v>
       </c>
       <c r="U54" s="4"/>
       <c r="V54" s="4"/>
@@ -7309,13 +7279,13 @@
     </row>
     <row r="55" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A55" s="18" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>322</v>
+        <v>317</v>
       </c>
       <c r="D55" s="32">
         <v>313</v>
@@ -7340,13 +7310,13 @@
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
       <c r="N55" s="4" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="O55" s="4" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="P55" s="4" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="Q55" s="4" t="s">
         <v>29</v>
@@ -7356,7 +7326,7 @@
         <v>26</v>
       </c>
       <c r="T55" s="4" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="U55" s="4"/>
       <c r="V55" s="4"/>
@@ -7370,13 +7340,13 @@
     </row>
     <row r="56" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A56" s="18" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="D56" s="32">
         <v>0</v>
@@ -7401,23 +7371,23 @@
       <c r="L56" s="4"/>
       <c r="M56" s="4"/>
       <c r="N56" s="4" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="O56" s="4" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="P56" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="Q56" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="R56" s="4"/>
       <c r="S56" s="4" t="s">
         <v>26</v>
       </c>
       <c r="T56" s="4" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="U56" s="4"/>
       <c r="V56" s="4"/>
@@ -7428,18 +7398,18 @@
         <v>28</v>
       </c>
       <c r="AA56" s="20" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
     </row>
     <row r="57" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A57" s="18" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="D57" s="32">
         <v>0</v>
@@ -7464,23 +7434,23 @@
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
       <c r="N57" s="4" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="O57" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="P57" s="4" t="s">
         <v>328</v>
       </c>
-      <c r="P57" s="4" t="s">
-        <v>333</v>
-      </c>
       <c r="Q57" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="R57" s="4"/>
       <c r="S57" s="4" t="s">
         <v>26</v>
       </c>
       <c r="T57" s="4" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="U57" s="4"/>
       <c r="V57" s="4"/>
@@ -7491,18 +7461,18 @@
         <v>28</v>
       </c>
       <c r="AA57" s="20" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
     </row>
     <row r="58" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A58" s="18" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="D58" s="32">
         <v>17973</v>
@@ -7527,13 +7497,13 @@
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
       <c r="N58" s="4" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="O58" s="4" t="s">
         <v>22</v>
       </c>
       <c r="P58" s="4" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="Q58" s="4" t="s">
         <v>29</v>
@@ -7543,7 +7513,7 @@
         <v>26</v>
       </c>
       <c r="T58" s="4" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="U58" s="4"/>
       <c r="V58" s="4"/>
@@ -7554,18 +7524,18 @@
         <v>28</v>
       </c>
       <c r="AA58" s="20" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
     </row>
     <row r="59" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A59" s="18" t="s">
-        <v>305</v>
+        <v>300</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="D59" s="32">
         <v>10306</v>
@@ -7590,13 +7560,13 @@
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
       <c r="N59" s="4" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="O59" s="4" t="s">
         <v>22</v>
       </c>
       <c r="P59" s="4" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="Q59" s="4" t="s">
         <v>29</v>
@@ -7606,7 +7576,7 @@
         <v>26</v>
       </c>
       <c r="T59" s="4" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="U59" s="4"/>
       <c r="V59" s="4"/>
@@ -7617,18 +7587,18 @@
         <v>28</v>
       </c>
       <c r="AA59" s="20" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
     </row>
     <row r="60" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A60" s="18" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="D60" s="32">
         <v>16</v>
@@ -7653,13 +7623,13 @@
       <c r="L60" s="4"/>
       <c r="M60" s="4"/>
       <c r="N60" s="4" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="O60" s="4" t="s">
         <v>22</v>
       </c>
       <c r="P60" s="4" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="Q60" s="4" t="s">
         <v>29</v>
@@ -7669,7 +7639,7 @@
         <v>26</v>
       </c>
       <c r="T60" s="4" t="s">
-        <v>355</v>
+        <v>350</v>
       </c>
       <c r="U60" s="4"/>
       <c r="V60" s="4"/>
@@ -7680,18 +7650,18 @@
         <v>28</v>
       </c>
       <c r="AA60" s="20" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
     </row>
     <row r="61" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A61" s="18" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="D61" s="32">
         <v>501</v>
@@ -7716,13 +7686,13 @@
       <c r="L61" s="4"/>
       <c r="M61" s="4"/>
       <c r="N61" s="4" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="O61" s="4" t="s">
         <v>22</v>
       </c>
       <c r="P61" s="4" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="Q61" s="4" t="s">
         <v>29</v>
@@ -7732,7 +7702,7 @@
         <v>26</v>
       </c>
       <c r="T61" s="4" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="U61" s="4"/>
       <c r="V61" s="4"/>
@@ -7743,18 +7713,18 @@
         <v>28</v>
       </c>
       <c r="AA61" s="20" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
     </row>
     <row r="62" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A62" s="18" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="D62" s="32">
         <v>9142</v>
@@ -7779,13 +7749,13 @@
       <c r="L62" s="4"/>
       <c r="M62" s="4"/>
       <c r="N62" s="4" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="O62" s="4" t="s">
         <v>22</v>
       </c>
       <c r="P62" s="4" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="Q62" s="4" t="s">
         <v>29</v>
@@ -7795,7 +7765,7 @@
         <v>26</v>
       </c>
       <c r="T62" s="4" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="U62" s="4"/>
       <c r="V62" s="4"/>
@@ -7806,18 +7776,18 @@
         <v>28</v>
       </c>
       <c r="AA62" s="20" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
     </row>
     <row r="63" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A63" s="18" t="s">
-        <v>321</v>
+        <v>316</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="D63" s="32">
         <v>9158</v>
@@ -7842,13 +7812,13 @@
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
       <c r="N63" s="4" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="O63" s="4" t="s">
         <v>22</v>
       </c>
       <c r="P63" s="4" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="Q63" s="4" t="s">
         <v>29</v>
@@ -7858,7 +7828,7 @@
         <v>26</v>
       </c>
       <c r="T63" s="4" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="U63" s="4"/>
       <c r="V63" s="4"/>
@@ -7869,18 +7839,18 @@
         <v>28</v>
       </c>
       <c r="AA63" s="20" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
     </row>
     <row r="64" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A64" s="18" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="D64" s="32">
         <v>4219</v>
@@ -7905,13 +7875,13 @@
       <c r="L64" s="4"/>
       <c r="M64" s="4"/>
       <c r="N64" s="4" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="O64" s="4" t="s">
         <v>22</v>
       </c>
       <c r="P64" s="4" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="Q64" s="4" t="s">
         <v>29</v>
@@ -7921,7 +7891,7 @@
         <v>26</v>
       </c>
       <c r="T64" s="4" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
       <c r="U64" s="4"/>
       <c r="V64" s="4"/>
@@ -7932,18 +7902,18 @@
         <v>28</v>
       </c>
       <c r="AA64" s="20" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
     </row>
     <row r="65" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A65" s="18" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
       <c r="D65" s="32">
         <v>2449</v>
@@ -7968,13 +7938,13 @@
       <c r="L65" s="4"/>
       <c r="M65" s="4"/>
       <c r="N65" s="4" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="O65" s="4" t="s">
         <v>22</v>
       </c>
       <c r="P65" s="4" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="Q65" s="4" t="s">
         <v>29</v>
@@ -7984,7 +7954,7 @@
         <v>26</v>
       </c>
       <c r="T65" s="4" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="U65" s="4"/>
       <c r="V65" s="4"/>
@@ -7995,18 +7965,18 @@
         <v>28</v>
       </c>
       <c r="AA65" s="20" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
     </row>
     <row r="66" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A66" s="18" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
       <c r="D66" s="32">
         <v>1457</v>
@@ -8031,13 +8001,13 @@
       <c r="L66" s="4"/>
       <c r="M66" s="4"/>
       <c r="N66" s="4" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="O66" s="4" t="s">
         <v>22</v>
       </c>
       <c r="P66" s="4" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
       <c r="Q66" s="4" t="s">
         <v>29</v>
@@ -8047,7 +8017,7 @@
         <v>26</v>
       </c>
       <c r="T66" s="4" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="U66" s="4"/>
       <c r="V66" s="4"/>
@@ -8058,18 +8028,18 @@
         <v>28</v>
       </c>
       <c r="AA66" s="20" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
     </row>
     <row r="67" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A67" s="18" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="D67" s="32">
         <v>1578</v>
@@ -8094,13 +8064,13 @@
       <c r="L67" s="4"/>
       <c r="M67" s="4"/>
       <c r="N67" s="4" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="O67" s="4" t="s">
         <v>22</v>
       </c>
       <c r="P67" s="4" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="Q67" s="4" t="s">
         <v>29</v>
@@ -8110,7 +8080,7 @@
         <v>26</v>
       </c>
       <c r="T67" s="4" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="U67" s="4"/>
       <c r="V67" s="4"/>
@@ -8121,18 +8091,18 @@
         <v>28</v>
       </c>
       <c r="AA67" s="20" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
     </row>
     <row r="68" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A68" s="18" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="D68" s="32">
         <v>792</v>
@@ -8157,13 +8127,13 @@
       <c r="L68" s="4"/>
       <c r="M68" s="4"/>
       <c r="N68" s="4" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="O68" s="4" t="s">
         <v>22</v>
       </c>
       <c r="P68" s="4" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
       <c r="Q68" s="4" t="s">
         <v>29</v>
@@ -8173,7 +8143,7 @@
         <v>26</v>
       </c>
       <c r="T68" s="4" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="U68" s="4"/>
       <c r="V68" s="4"/>
@@ -8184,18 +8154,18 @@
         <v>28</v>
       </c>
       <c r="AA68" s="20" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
     </row>
     <row r="69" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A69" s="18" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="D69" s="32">
         <v>1</v>
@@ -8220,13 +8190,13 @@
       <c r="L69" s="4"/>
       <c r="M69" s="4"/>
       <c r="N69" s="4" t="s">
-        <v>361</v>
+        <v>356</v>
       </c>
       <c r="O69" s="4" t="s">
         <v>22</v>
       </c>
       <c r="P69" s="4" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="Q69" s="4" t="s">
         <v>29</v>
@@ -8236,7 +8206,7 @@
         <v>26</v>
       </c>
       <c r="T69" s="4" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="U69" s="4"/>
       <c r="V69" s="4"/>
@@ -8247,18 +8217,18 @@
         <v>28</v>
       </c>
       <c r="AA69" s="20" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
     </row>
     <row r="70" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A70" s="18" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="D70" s="32">
         <v>2204</v>
@@ -8283,13 +8253,13 @@
       <c r="L70" s="4"/>
       <c r="M70" s="4"/>
       <c r="N70" s="4" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="O70" s="4" t="s">
         <v>22</v>
       </c>
       <c r="P70" s="4" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="Q70" s="4" t="s">
         <v>29</v>
@@ -8299,7 +8269,7 @@
         <v>26</v>
       </c>
       <c r="T70" s="4" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="U70" s="4"/>
       <c r="V70" s="4"/>
@@ -8310,18 +8280,18 @@
         <v>28</v>
       </c>
       <c r="AA70" s="20" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="71" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A71" s="18" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="D71" s="32">
         <v>61</v>
@@ -8346,13 +8316,13 @@
       <c r="L71" s="4"/>
       <c r="M71" s="4"/>
       <c r="N71" s="4" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="O71" s="4" t="s">
         <v>22</v>
       </c>
       <c r="P71" s="4" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="Q71" s="4" t="s">
         <v>29</v>
@@ -8362,7 +8332,7 @@
         <v>26</v>
       </c>
       <c r="T71" s="4" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="U71" s="4"/>
       <c r="V71" s="4"/>
@@ -8373,18 +8343,18 @@
         <v>28</v>
       </c>
       <c r="AA71" s="20" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="72" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A72" s="18" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="D72" s="32">
         <v>1535</v>
@@ -8409,13 +8379,13 @@
       <c r="L72" s="4"/>
       <c r="M72" s="4"/>
       <c r="N72" s="4" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="O72" s="4" t="s">
         <v>22</v>
       </c>
       <c r="P72" s="4" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="Q72" s="4" t="s">
         <v>29</v>
@@ -8425,7 +8395,7 @@
         <v>26</v>
       </c>
       <c r="T72" s="4" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="U72" s="4"/>
       <c r="V72" s="4"/>
@@ -8436,18 +8406,18 @@
         <v>28</v>
       </c>
       <c r="AA72" s="20" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="73" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A73" s="18" t="s">
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="D73" s="32">
         <v>666</v>
@@ -8472,13 +8442,13 @@
       <c r="L73" s="4"/>
       <c r="M73" s="4"/>
       <c r="N73" s="4" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="O73" s="4" t="s">
         <v>22</v>
       </c>
       <c r="P73" s="4" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="Q73" s="4" t="s">
         <v>29</v>
@@ -8488,7 +8458,7 @@
         <v>26</v>
       </c>
       <c r="T73" s="4" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="U73" s="4"/>
       <c r="V73" s="4"/>
@@ -8499,18 +8469,18 @@
         <v>28</v>
       </c>
       <c r="AA73" s="20" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="74" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A74" s="18" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="D74" s="32">
         <v>18500</v>
@@ -8535,13 +8505,13 @@
       <c r="L74" s="4"/>
       <c r="M74" s="4"/>
       <c r="N74" s="4" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="O74" s="4" t="s">
         <v>22</v>
       </c>
       <c r="P74" s="4" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="Q74" s="4" t="s">
         <v>29</v>
@@ -8551,7 +8521,7 @@
         <v>26</v>
       </c>
       <c r="T74" s="4" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="U74" s="4"/>
       <c r="V74" s="4"/>
@@ -8562,18 +8532,18 @@
         <v>28</v>
       </c>
       <c r="AA74" s="20" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="75" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A75" s="18" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="B75" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="D75" s="32">
         <v>876</v>
@@ -8598,13 +8568,13 @@
       <c r="L75" s="4"/>
       <c r="M75" s="4"/>
       <c r="N75" s="4" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="O75" s="4" t="s">
         <v>22</v>
       </c>
       <c r="P75" s="4" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="Q75" s="4" t="s">
         <v>29</v>
@@ -8614,7 +8584,7 @@
         <v>26</v>
       </c>
       <c r="T75" s="4" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="U75" s="4"/>
       <c r="V75" s="4"/>
@@ -8625,18 +8595,18 @@
         <v>28</v>
       </c>
       <c r="AA75" s="20" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="76" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A76" s="18" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
       <c r="D76" s="32">
         <v>74</v>
@@ -8661,13 +8631,13 @@
       <c r="L76" s="4"/>
       <c r="M76" s="4"/>
       <c r="N76" s="4" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="O76" s="4" t="s">
         <v>22</v>
       </c>
       <c r="P76" s="4" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="Q76" s="4" t="s">
         <v>29</v>
@@ -8677,7 +8647,7 @@
         <v>26</v>
       </c>
       <c r="T76" s="4" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="U76" s="4"/>
       <c r="V76" s="4"/>
@@ -8688,18 +8658,18 @@
         <v>28</v>
       </c>
       <c r="AA76" s="20" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="77" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A77" s="18" t="s">
-        <v>360</v>
+        <v>355</v>
       </c>
       <c r="B77" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="D77" s="32">
         <v>722</v>
@@ -8724,13 +8694,13 @@
       <c r="L77" s="4"/>
       <c r="M77" s="4"/>
       <c r="N77" s="4" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="O77" s="4" t="s">
         <v>22</v>
       </c>
       <c r="P77" s="4" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="Q77" s="4" t="s">
         <v>29</v>
@@ -8740,7 +8710,7 @@
         <v>26</v>
       </c>
       <c r="T77" s="4" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="U77" s="4"/>
       <c r="V77" s="4"/>
@@ -8751,18 +8721,18 @@
         <v>28</v>
       </c>
       <c r="AA77" s="20" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="78" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A78" s="18" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="D78" s="32">
         <v>4158</v>
@@ -8787,13 +8757,13 @@
       <c r="L78" s="4"/>
       <c r="M78" s="4"/>
       <c r="N78" s="4" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="O78" s="4" t="s">
         <v>22</v>
       </c>
       <c r="P78" s="4" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="Q78" s="4" t="s">
         <v>29</v>
@@ -8803,7 +8773,7 @@
         <v>26</v>
       </c>
       <c r="T78" s="4" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="U78" s="4"/>
       <c r="V78" s="4"/>
@@ -8814,18 +8784,18 @@
         <v>28</v>
       </c>
       <c r="AA78" s="20" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="79" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A79" s="18" t="s">
-        <v>370</v>
+        <v>365</v>
       </c>
       <c r="B79" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="D79" s="32">
         <v>954</v>
@@ -8850,13 +8820,13 @@
       <c r="L79" s="4"/>
       <c r="M79" s="4"/>
       <c r="N79" s="4" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="O79" s="4" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="P79" s="4" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="Q79" s="4" t="s">
         <v>29</v>
@@ -8866,7 +8836,7 @@
         <v>26</v>
       </c>
       <c r="T79" s="4" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="U79" s="4"/>
       <c r="V79" s="4"/>
@@ -8877,18 +8847,18 @@
         <v>28</v>
       </c>
       <c r="AA79" s="20" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
     </row>
     <row r="80" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A80" s="18" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="D80" s="32">
         <v>912</v>
@@ -8913,13 +8883,13 @@
       <c r="L80" s="4"/>
       <c r="M80" s="4"/>
       <c r="N80" s="4" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="O80" s="4" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="P80" s="4" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="Q80" s="4" t="s">
         <v>29</v>
@@ -8929,7 +8899,7 @@
         <v>26</v>
       </c>
       <c r="T80" s="4" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="U80" s="4"/>
       <c r="V80" s="4"/>
@@ -8940,18 +8910,18 @@
         <v>28</v>
       </c>
       <c r="AA80" s="20" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
     </row>
     <row r="81" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A81" s="18" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
       <c r="B81" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="D81" s="32">
         <v>6364</v>
@@ -8976,13 +8946,13 @@
       <c r="L81" s="4"/>
       <c r="M81" s="4"/>
       <c r="N81" s="4" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="O81" s="4" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="P81" s="4" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="Q81" s="4" t="s">
         <v>29</v>
@@ -8992,7 +8962,7 @@
         <v>26</v>
       </c>
       <c r="T81" s="4" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="U81" s="4"/>
       <c r="V81" s="4"/>
@@ -9003,18 +8973,18 @@
         <v>28</v>
       </c>
       <c r="AA81" s="20" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
     </row>
     <row r="82" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A82" s="18" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="D82" s="32">
         <v>0</v>
@@ -9039,13 +9009,13 @@
       <c r="L82" s="4"/>
       <c r="M82" s="4"/>
       <c r="N82" s="4" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="O82" s="4" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="P82" s="4" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="Q82" s="4" t="s">
         <v>29</v>
@@ -9055,7 +9025,7 @@
         <v>26</v>
       </c>
       <c r="T82" s="4" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="U82" s="4"/>
       <c r="V82" s="4"/>
@@ -9066,18 +9036,18 @@
         <v>28</v>
       </c>
       <c r="AA82" s="20" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="83" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A83" s="18" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
       <c r="B83" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="D83" s="32">
         <v>410</v>
@@ -9102,13 +9072,13 @@
       <c r="L83" s="4"/>
       <c r="M83" s="4"/>
       <c r="N83" s="4" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="O83" s="4" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="P83" s="4" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="Q83" s="4" t="s">
         <v>29</v>
@@ -9118,7 +9088,7 @@
         <v>26</v>
       </c>
       <c r="T83" s="4" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="U83" s="4"/>
       <c r="V83" s="4"/>
@@ -9129,18 +9099,18 @@
         <v>28</v>
       </c>
       <c r="AA83" s="20" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
     </row>
     <row r="84" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A84" s="18" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="D84" s="32">
         <v>31</v>
@@ -9165,13 +9135,13 @@
       <c r="L84" s="4"/>
       <c r="M84" s="4"/>
       <c r="N84" s="4" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="O84" s="4" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="P84" s="4" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="Q84" s="4" t="s">
         <v>29</v>
@@ -9181,7 +9151,7 @@
         <v>26</v>
       </c>
       <c r="T84" s="4" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="U84" s="4"/>
       <c r="V84" s="4"/>
@@ -9192,18 +9162,18 @@
         <v>28</v>
       </c>
       <c r="AA84" s="20" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="85" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A85" s="18" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="B85" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="D85" s="32">
         <v>64</v>
@@ -9228,13 +9198,13 @@
       <c r="L85" s="4"/>
       <c r="M85" s="4"/>
       <c r="N85" s="4" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="O85" s="4" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="P85" s="4" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="Q85" s="4" t="s">
         <v>29</v>
@@ -9244,7 +9214,7 @@
         <v>26</v>
       </c>
       <c r="T85" s="4" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="U85" s="4"/>
       <c r="V85" s="4"/>
@@ -9255,18 +9225,18 @@
         <v>28</v>
       </c>
       <c r="AA85" s="20" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="86" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A86" s="18" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="D86" s="32">
         <v>26</v>
@@ -9291,13 +9261,13 @@
       <c r="L86" s="4"/>
       <c r="M86" s="4"/>
       <c r="N86" s="4" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="O86" s="4" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="P86" s="4" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="Q86" s="4" t="s">
         <v>29</v>
@@ -9307,7 +9277,7 @@
         <v>26</v>
       </c>
       <c r="T86" s="4" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="U86" s="4"/>
       <c r="V86" s="4"/>
@@ -9318,18 +9288,18 @@
         <v>28</v>
       </c>
       <c r="AA86" s="20" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="87" spans="1:27" ht="30" x14ac:dyDescent="0.25">
       <c r="A87" s="18" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="B87" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="D87" s="32">
         <v>2516</v>
@@ -9354,13 +9324,13 @@
       <c r="L87" s="4"/>
       <c r="M87" s="4"/>
       <c r="N87" s="4" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="O87" s="4" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="P87" s="4" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="Q87" s="4" t="s">
         <v>29</v>
@@ -9370,7 +9340,7 @@
         <v>26</v>
       </c>
       <c r="T87" s="4" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="U87" s="4"/>
       <c r="V87" s="4"/>
@@ -9381,18 +9351,18 @@
         <v>28</v>
       </c>
       <c r="AA87" s="20" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
     </row>
     <row r="88" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A88" s="18" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="D88" s="32">
         <v>1139</v>
@@ -9417,16 +9387,16 @@
       <c r="L88" s="4"/>
       <c r="M88" s="4"/>
       <c r="N88" s="4" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="O88" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P88" s="4" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="Q88" s="4" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="R88" s="4" t="s">
         <v>42</v>
@@ -9435,7 +9405,7 @@
         <v>26</v>
       </c>
       <c r="T88" s="4" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="U88" s="4"/>
       <c r="V88" s="4"/>
@@ -9446,18 +9416,18 @@
         <v>28</v>
       </c>
       <c r="AA88" s="20" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="89" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A89" s="18" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="B89" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="D89" s="32">
         <v>183</v>
@@ -9482,16 +9452,16 @@
       <c r="L89" s="4"/>
       <c r="M89" s="4"/>
       <c r="N89" s="4" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="O89" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P89" s="4" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="Q89" s="4" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="R89" s="4" t="s">
         <v>42</v>
@@ -9500,7 +9470,7 @@
         <v>26</v>
       </c>
       <c r="T89" s="4" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="U89" s="4"/>
       <c r="V89" s="4"/>
@@ -9511,18 +9481,18 @@
         <v>28</v>
       </c>
       <c r="AA89" s="20" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="90" spans="1:27" ht="30" x14ac:dyDescent="0.25">
       <c r="A90" s="18" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="D90" s="32">
         <v>392</v>
@@ -9545,13 +9515,13 @@
       <c r="L90" s="4"/>
       <c r="M90" s="4"/>
       <c r="N90" s="4" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="O90" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="P90" s="4" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="Q90" s="4" t="s">
         <v>29</v>
@@ -9563,7 +9533,7 @@
         <v>26</v>
       </c>
       <c r="T90" s="4" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="U90" s="4"/>
       <c r="V90" s="4"/>
@@ -9574,18 +9544,18 @@
         <v>28</v>
       </c>
       <c r="AA90" s="20" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
     </row>
     <row r="91" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A91" s="18" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="D91" s="32">
         <v>4897</v>
@@ -9610,23 +9580,23 @@
       <c r="L91" s="4"/>
       <c r="M91" s="4"/>
       <c r="N91" s="4" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="O91" s="4" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="P91" s="4" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="Q91" s="4" t="s">
         <v>29</v>
       </c>
       <c r="R91" s="4"/>
       <c r="S91" s="4" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="T91" s="4" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="U91" s="4"/>
       <c r="V91" s="4"/>
@@ -9637,18 +9607,18 @@
         <v>28</v>
       </c>
       <c r="AA91" s="20" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
     </row>
     <row r="92" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A92" s="18" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="D92" s="32">
         <v>1256</v>
@@ -9673,23 +9643,23 @@
       <c r="L92" s="4"/>
       <c r="M92" s="4"/>
       <c r="N92" s="4" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="O92" s="4" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="P92" s="4" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="Q92" s="4" t="s">
         <v>29</v>
       </c>
       <c r="R92" s="4"/>
       <c r="S92" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="T92" s="4" t="s">
         <v>494</v>
-      </c>
-      <c r="T92" s="4" t="s">
-        <v>499</v>
       </c>
       <c r="U92" s="4"/>
       <c r="V92" s="4"/>
@@ -9700,18 +9670,18 @@
         <v>28</v>
       </c>
       <c r="AA92" s="20" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
     </row>
     <row r="93" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A93" s="18" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="D93" s="32">
         <v>1150</v>
@@ -9736,13 +9706,13 @@
       <c r="L93" s="4"/>
       <c r="M93" s="4"/>
       <c r="N93" s="4" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="O93" s="4" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="P93" s="4" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="Q93" s="4" t="s">
         <v>29</v>
@@ -9751,10 +9721,10 @@
         <v>42</v>
       </c>
       <c r="S93" s="4" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="T93" s="4" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="U93" s="4"/>
       <c r="V93" s="4"/>
@@ -9768,13 +9738,13 @@
     </row>
     <row r="94" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A94" s="18" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="B94" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="D94" s="32">
         <v>106</v>
@@ -9799,23 +9769,23 @@
       <c r="L94" s="4"/>
       <c r="M94" s="4"/>
       <c r="N94" s="4" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="O94" s="4" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="P94" s="4" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="Q94" s="4" t="s">
         <v>29</v>
       </c>
       <c r="R94" s="4"/>
       <c r="S94" s="4" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="T94" s="4" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="U94" s="4"/>
       <c r="V94" s="4"/>
@@ -9829,13 +9799,13 @@
     </row>
     <row r="95" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A95" s="18" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="B95" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="D95" s="32">
         <v>2163</v>
@@ -9860,13 +9830,13 @@
       <c r="L95" s="4"/>
       <c r="M95" s="4"/>
       <c r="N95" s="4" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="O95" s="4" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="P95" s="4" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="Q95" s="4" t="s">
         <v>29</v>
@@ -9875,10 +9845,10 @@
         <v>42</v>
       </c>
       <c r="S95" s="4" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="T95" s="4" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="U95" s="4"/>
       <c r="V95" s="4"/>
@@ -9889,18 +9859,18 @@
         <v>28</v>
       </c>
       <c r="AA95" s="20" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
     </row>
     <row r="96" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A96" s="18" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="B96" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="D96" s="32">
         <v>463</v>
@@ -9925,23 +9895,23 @@
       <c r="L96" s="4"/>
       <c r="M96" s="4"/>
       <c r="N96" s="4" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="O96" s="4" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="P96" s="4" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="Q96" s="4" t="s">
         <v>29</v>
       </c>
       <c r="R96" s="4"/>
       <c r="S96" s="4" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="T96" s="4" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="U96" s="4"/>
       <c r="V96" s="4"/>
@@ -9955,13 +9925,13 @@
     </row>
     <row r="97" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A97" s="18" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="B97" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="D97" s="32">
         <v>1700</v>
@@ -9986,23 +9956,23 @@
       <c r="L97" s="4"/>
       <c r="M97" s="4"/>
       <c r="N97" s="4" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="O97" s="4" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="P97" s="4" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="Q97" s="4" t="s">
         <v>29</v>
       </c>
       <c r="R97" s="4"/>
       <c r="S97" s="4" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="T97" s="4" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="U97" s="4"/>
       <c r="V97" s="4"/>
@@ -10016,13 +9986,13 @@
     </row>
     <row r="98" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A98" s="18" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="B98" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C98" s="3" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="D98" s="32">
         <v>1478</v>
@@ -10047,13 +10017,13 @@
       <c r="L98" s="4"/>
       <c r="M98" s="4"/>
       <c r="N98" s="4" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="O98" s="4" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="P98" s="4" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="Q98" s="4" t="s">
         <v>29</v>
@@ -10062,10 +10032,10 @@
         <v>42</v>
       </c>
       <c r="S98" s="4" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="T98" s="4" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="U98" s="4"/>
       <c r="V98" s="4"/>
@@ -10076,18 +10046,18 @@
         <v>28</v>
       </c>
       <c r="AA98" s="20" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
     </row>
     <row r="99" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A99" s="18" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="B99" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="D99" s="32">
         <v>630</v>
@@ -10112,23 +10082,23 @@
       <c r="L99" s="4"/>
       <c r="M99" s="4"/>
       <c r="N99" s="4" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="O99" s="4" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="P99" s="4" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="Q99" s="4" t="s">
         <v>29</v>
       </c>
       <c r="R99" s="4"/>
       <c r="S99" s="4" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="T99" s="4" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="U99" s="4"/>
       <c r="V99" s="4"/>
@@ -10142,13 +10112,13 @@
     </row>
     <row r="100" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A100" s="18" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="B100" s="3" t="s">
         <v>34</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="D100" s="32">
         <v>848</v>
@@ -10173,23 +10143,23 @@
       <c r="L100" s="4"/>
       <c r="M100" s="4"/>
       <c r="N100" s="4" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="O100" s="4" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="P100" s="4" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="Q100" s="4" t="s">
         <v>29</v>
       </c>
       <c r="R100" s="4"/>
       <c r="S100" s="4" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="T100" s="4" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="U100" s="4"/>
       <c r="V100" s="4"/>
@@ -10203,30 +10173,30 @@
     </row>
     <row r="101" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A101" s="26" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="B101" s="27" t="s">
         <v>34</v>
       </c>
       <c r="C101" s="27" t="s">
-        <v>527</v>
-      </c>
-      <c r="D101" s="59">
-        <v>0</v>
-      </c>
-      <c r="E101" s="59">
-        <v>0</v>
-      </c>
-      <c r="F101" s="59">
-        <v>0</v>
-      </c>
-      <c r="G101" s="59">
+        <v>522</v>
+      </c>
+      <c r="D101" s="49">
+        <v>0</v>
+      </c>
+      <c r="E101" s="49">
+        <v>0</v>
+      </c>
+      <c r="F101" s="49">
+        <v>0</v>
+      </c>
+      <c r="G101" s="49">
         <v>18</v>
       </c>
-      <c r="H101" s="59">
+      <c r="H101" s="49">
         <v>65</v>
       </c>
-      <c r="I101" s="59">
+      <c r="I101" s="49">
         <v>61</v>
       </c>
       <c r="J101" s="28"/>
@@ -10234,23 +10204,23 @@
       <c r="L101" s="28"/>
       <c r="M101" s="28"/>
       <c r="N101" s="28" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="O101" s="28" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="P101" s="28" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="Q101" s="28" t="s">
         <v>29</v>
       </c>
       <c r="R101" s="28"/>
       <c r="S101" s="28" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="T101" s="28" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="U101" s="28"/>
       <c r="V101" s="28"/>
@@ -10323,10 +10293,10 @@
   <sheetData>
     <row r="1" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
     </row>
     <row r="3" spans="1:27" s="13" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
@@ -11727,7 +11697,7 @@
         <v>Goal 3: Strengthen Persistence, Retention, and Momentum</v>
       </c>
       <c r="W19" s="30" t="str">
-        <v>1: Success</v>
+        <v>Goal 1: Success</v>
       </c>
       <c r="X19" s="30" t="str">
         <v>1.3 Improve course success rates</v>
@@ -12474,7 +12444,7 @@
         <v>Goal 4: Accelerate Completion, Credential Attainment, and Transfer</v>
       </c>
       <c r="W28" s="30" t="str">
-        <v>1: Success</v>
+        <v>Goal 1: Success</v>
       </c>
       <c r="X28" s="30" t="str">
         <v>1.2 Reduce time to degree and certificate attainment</v>
@@ -12806,7 +12776,7 @@
         <v>Goal 4: Accelerate Completion, Credential Attainment, and Transfer</v>
       </c>
       <c r="W32" s="30" t="str">
-        <v>3: Career</v>
+        <v>Goal 3: Career</v>
       </c>
       <c r="X32" s="30" t="str">
         <v>3.1 Align programs with regional workforce needs</v>
@@ -12849,17 +12819,17 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">

--- a/unified_plan_metrics_template.xlsx
+++ b/unified_plan_metrics_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chaffeyccd-my.sharepoint.com/personal/joseph_cascio_chaffey_edu/Documents/Research Analyst/Surveys and Reports/Combining Initiative Reports/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://chaffeyccd-my.sharepoint.com/personal/joseph_cascio_chaffey_edu/Documents/Desktop/Dashboards/Plan Metrics Dashboard/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="435" documentId="8_{0966D836-5100-49BC-8A45-6686B0C0AF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F6475197-4B75-4748-AD3B-1CB5A3E6C027}"/>
+  <xr:revisionPtr revIDLastSave="436" documentId="8_{0966D836-5100-49BC-8A45-6686B0C0AF40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13D647DB-FF79-4BD1-9D4F-8D1789A2B7AE}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BFF79AE2-E76B-441F-B8D7-30B63CE1804C}"/>
   </bookViews>
@@ -1047,9 +1047,6 @@
     <t>Strategic Plan Target Goal (By 2030)</t>
   </si>
   <si>
-    <t>EMP Target Goal (By YYYY)</t>
-  </si>
-  <si>
     <t>IR Dashboard - Enrollment Management</t>
   </si>
   <si>
@@ -1111,6 +1108,9 @@
   </si>
   <si>
     <t>CCFS-320 Report</t>
+  </si>
+  <si>
+    <t>EMP Target Goal (By 2030)</t>
   </si>
 </sst>
 </file>
@@ -1740,7 +1740,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -1911,15 +1911,6 @@
     <xf numFmtId="0" fontId="16" fillId="37" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="20" builtinId="30" customBuiltin="1"/>
@@ -2729,7 +2720,7 @@
     <tableColumn id="9" xr3:uid="{F5EAFEFD-FC0A-487F-8525-1C93255BD17F}" name="2025-2026" dataDxfId="24"/>
     <tableColumn id="28" xr3:uid="{71F30DCF-07A1-4BBA-8536-EA45043CB21E}" name="Date Pulled" dataDxfId="23" dataCellStyle="Percent"/>
     <tableColumn id="22" xr3:uid="{19854763-5938-48CE-8523-23258BFF1C3E}" name="EMP Baseline (2025-2026 Yr 0)" dataDxfId="22"/>
-    <tableColumn id="23" xr3:uid="{14F0D8E9-D836-4B80-94D3-7B8418392D1A}" name="EMP Target Goal (By YYYY)" dataDxfId="21"/>
+    <tableColumn id="23" xr3:uid="{14F0D8E9-D836-4B80-94D3-7B8418392D1A}" name="EMP Target Goal (By 2030)" dataDxfId="21"/>
     <tableColumn id="24" xr3:uid="{FA021FCD-2B93-4B93-B866-74FFE5B66D07}" name="Strategic Plan Baseline (2024-2025 Yr 0)" dataDxfId="20"/>
     <tableColumn id="25" xr3:uid="{D5AB3269-32D4-42B9-BB3A-AA4B7E4FFDFF}" name="Strategic Plan Target Goal (By 2030)" dataDxfId="19"/>
     <tableColumn id="10" xr3:uid="{75661E75-33EF-41F7-82E4-B6310A3593CE}" name="Metric Category(s) (Values separated with &quot;;&quot;)" dataDxfId="18"/>
@@ -3143,13 +3134,13 @@
         <v>14</v>
       </c>
       <c r="K1" s="55" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="L1" s="22" t="s">
         <v>15</v>
       </c>
       <c r="M1" s="49" t="s">
-        <v>309</v>
+        <v>330</v>
       </c>
       <c r="N1" s="22" t="s">
         <v>16</v>
@@ -3173,16 +3164,16 @@
         <v>113</v>
       </c>
       <c r="U1" s="59" t="s">
+        <v>324</v>
+      </c>
+      <c r="V1" s="59" t="s">
         <v>325</v>
       </c>
-      <c r="V1" s="59" t="s">
+      <c r="W1" s="59" t="s">
         <v>326</v>
       </c>
-      <c r="W1" s="59" t="s">
+      <c r="X1" s="59" t="s">
         <v>327</v>
-      </c>
-      <c r="X1" s="59" t="s">
-        <v>328</v>
       </c>
       <c r="Y1" s="22" t="s">
         <v>6</v>
@@ -3305,17 +3296,17 @@
       </c>
     </row>
     <row r="3" spans="1:33" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="60" t="s">
+      <c r="A3" s="17" t="s">
+        <v>328</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>329</v>
-      </c>
-      <c r="B3" s="61" t="s">
-        <v>244</v>
-      </c>
-      <c r="C3" s="61" t="s">
-        <v>302</v>
-      </c>
-      <c r="D3" s="62" t="s">
-        <v>330</v>
       </c>
       <c r="E3" s="15">
         <v>14513.1</v>
@@ -4117,7 +4108,7 @@
         <v>82</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E12" s="39">
         <v>0.81299999999999994</v>
@@ -4209,7 +4200,7 @@
         <v>91</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E13" s="38">
         <v>13.41</v>
@@ -4301,7 +4292,7 @@
         <v>96</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E14" s="40">
         <v>0.96099999999999997</v>
@@ -4389,7 +4380,7 @@
         <v>104</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E15" s="40">
         <v>3.1E-2</v>
@@ -4477,7 +4468,7 @@
         <v>109</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E16" s="36">
         <v>0.70199999999999996</v>
@@ -4581,7 +4572,7 @@
         <v>116</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E17" s="40">
         <v>0.91500000000000004</v>
@@ -4677,7 +4668,7 @@
         <v>121</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E18" s="40">
         <v>0.69799999999999995</v>
@@ -4757,17 +4748,17 @@
       </c>
     </row>
     <row r="19" spans="1:33" ht="90" x14ac:dyDescent="0.25">
-      <c r="A19" s="60" t="s">
+      <c r="A19" s="17" t="s">
         <v>301</v>
       </c>
-      <c r="B19" s="61" t="s">
+      <c r="B19" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="C19" s="61" t="s">
+      <c r="C19" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="D19" s="62" t="s">
-        <v>312</v>
+      <c r="D19" s="4" t="s">
+        <v>311</v>
       </c>
       <c r="E19" s="36">
         <v>0.68100000000000005</v>
@@ -5136,7 +5127,7 @@
     </row>
     <row r="23" spans="1:33" ht="120" x14ac:dyDescent="0.25">
       <c r="A23" s="18" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>244</v>
@@ -5145,7 +5136,7 @@
         <v>151</v>
       </c>
       <c r="D23" s="44" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E23" s="42"/>
       <c r="F23" s="42"/>
@@ -5220,7 +5211,7 @@
     </row>
     <row r="24" spans="1:33" ht="120" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>244</v>
@@ -5229,7 +5220,7 @@
         <v>151</v>
       </c>
       <c r="D24" s="44" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="E24" s="42">
         <v>593</v>
@@ -5871,7 +5862,7 @@
         <v>174</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="E31" s="43">
         <v>84.2</v>
@@ -5968,10 +5959,10 @@
         <v>244</v>
       </c>
       <c r="C32" s="4" t="s">
+        <v>321</v>
+      </c>
+      <c r="D32" s="4" t="s">
         <v>322</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>323</v>
       </c>
       <c r="E32" s="43">
         <v>83.6</v>
@@ -6067,7 +6058,7 @@
         <v>185</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="E33" s="43">
         <v>86.4</v>
@@ -6251,7 +6242,7 @@
         <v>303</v>
       </c>
       <c r="D35" s="44" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="E35" s="42">
         <v>2218</v>
@@ -6345,7 +6336,7 @@
         <v>194</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="E36" s="26">
         <v>2648</v>
@@ -6443,7 +6434,7 @@
         <v>201</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="E37" s="26">
         <v>2581</v>
@@ -7047,7 +7038,7 @@
         <v>EMP Baseline (2025-2026 Yr 0)</v>
       </c>
       <c r="M3" s="11" t="str">
-        <v>EMP Target Goal (By YYYY)</v>
+        <v>EMP Target Goal (By 2030)</v>
       </c>
       <c r="N3" s="11" t="str">
         <v>Strategic Plan Baseline (2024-2025 Yr 0)</v>
